--- a/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
+++ b/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\StaticDynamicAnalysis\ida-spo-msa\HazardAnalysis\gm-selection\2020_NBC_MyCopy_new-main\GMSelection_NGA_KiK_mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B301DBE0-4930-45F5-90A8-CF119CF43327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF958599-258A-461E-B668-ADC8B2EA4EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GMSel_ΔM (±)" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="43">
   <si>
     <t>SNo</t>
   </si>
@@ -46,201 +46,6 @@
   </si>
   <si>
     <t>SF</t>
-  </si>
-  <si>
-    <t>EQID{70011} = '1166';</t>
-  </si>
-  <si>
-    <t>EQID{70012} = '1166';</t>
-  </si>
-  <si>
-    <t>EQID{70021} = '1286';</t>
-  </si>
-  <si>
-    <t>EQID{70022} = '1286';</t>
-  </si>
-  <si>
-    <t>EQID{70031} = '1292';</t>
-  </si>
-  <si>
-    <t>EQID{70032} = '1292';</t>
-  </si>
-  <si>
-    <t>EQID{70041} = '1297';</t>
-  </si>
-  <si>
-    <t>EQID{70042} = '1297';</t>
-  </si>
-  <si>
-    <t>EQID{70051} = '14';</t>
-  </si>
-  <si>
-    <t>EQID{70052} = '14';</t>
-  </si>
-  <si>
-    <t>EQID{70061} = '1436';</t>
-  </si>
-  <si>
-    <t>EQID{70062} = '1436';</t>
-  </si>
-  <si>
-    <t>EQID{70071} = '1465';</t>
-  </si>
-  <si>
-    <t>EQID{70072} = '1465';</t>
-  </si>
-  <si>
-    <t>EQID{70081} = '1469';</t>
-  </si>
-  <si>
-    <t>EQID{70082} = '1469';</t>
-  </si>
-  <si>
-    <t>EQID{70091} = '1470';</t>
-  </si>
-  <si>
-    <t>EQID{70092} = '1470';</t>
-  </si>
-  <si>
-    <t>EQID{70101} = '1472';</t>
-  </si>
-  <si>
-    <t>EQID{70102} = '1472';</t>
-  </si>
-  <si>
-    <t>EQID{70111} = '1478';</t>
-  </si>
-  <si>
-    <t>EQID{70112} = '1478';</t>
-  </si>
-  <si>
-    <t>EQID{70121} = '1485';</t>
-  </si>
-  <si>
-    <t>EQID{70122} = '1485';</t>
-  </si>
-  <si>
-    <t>EQID{70131} = '1487';</t>
-  </si>
-  <si>
-    <t>EQID{70132} = '1487';</t>
-  </si>
-  <si>
-    <t>EQID{70141} = '1524';</t>
-  </si>
-  <si>
-    <t>EQID{70142} = '1524';</t>
-  </si>
-  <si>
-    <t>EQID{70151} = '1555';</t>
-  </si>
-  <si>
-    <t>EQID{70152} = '1555';</t>
-  </si>
-  <si>
-    <t>EQID{70161} = '1557';</t>
-  </si>
-  <si>
-    <t>EQID{70162} = '1557';</t>
-  </si>
-  <si>
-    <t>EQID{70171} = '1575';</t>
-  </si>
-  <si>
-    <t>EQID{70172} = '1575';</t>
-  </si>
-  <si>
-    <t>EQID{70181} = '1581';</t>
-  </si>
-  <si>
-    <t>EQID{70182} = '1581';</t>
-  </si>
-  <si>
-    <t>EQID{70191} = '2466';</t>
-  </si>
-  <si>
-    <t>EQID{70192} = '2466';</t>
-  </si>
-  <si>
-    <t>EQID{70201} = '3274';</t>
-  </si>
-  <si>
-    <t>EQID{70202} = '3274';</t>
-  </si>
-  <si>
-    <t>EQID{70211} = '3281';</t>
-  </si>
-  <si>
-    <t>EQID{70212} = '3281';</t>
-  </si>
-  <si>
-    <t>EQID{70221} = '3307';</t>
-  </si>
-  <si>
-    <t>EQID{70222} = '3307';</t>
-  </si>
-  <si>
-    <t>EQID{70231} = '3750';</t>
-  </si>
-  <si>
-    <t>EQID{70232} = '3750';</t>
-  </si>
-  <si>
-    <t>EQID{70241} = '3751';</t>
-  </si>
-  <si>
-    <t>EQID{70242} = '3751';</t>
-  </si>
-  <si>
-    <t>EQID{70251} = '4350';</t>
-  </si>
-  <si>
-    <t>EQID{70252} = '4350';</t>
-  </si>
-  <si>
-    <t>EQID{70261} = '4884';</t>
-  </si>
-  <si>
-    <t>EQID{70262} = '4884';</t>
-  </si>
-  <si>
-    <t>EQID{70271} = '5663';</t>
-  </si>
-  <si>
-    <t>EQID{70272} = '5663';</t>
-  </si>
-  <si>
-    <t>EQID{70281} = '5778';</t>
-  </si>
-  <si>
-    <t>EQID{70282} = '5778';</t>
-  </si>
-  <si>
-    <t>EQID{70291} = '78';</t>
-  </si>
-  <si>
-    <t>EQID{70292} = '78';</t>
-  </si>
-  <si>
-    <t>EQID{70301} = '963';</t>
-  </si>
-  <si>
-    <t>EQID{70302} = '963';</t>
-  </si>
-  <si>
-    <t>GMSelection_Format</t>
-  </si>
-  <si>
-    <t>After 5% Trim</t>
-  </si>
-  <si>
-    <t>100 sec</t>
-  </si>
-  <si>
-    <t>200 sec</t>
-  </si>
-  <si>
-    <t>BCH16</t>
   </si>
   <si>
     <t>CY14</t>
@@ -262,12 +67,6 @@
   </si>
   <si>
     <t>1) RSN 5663 is not selected in CY14 and ASK14</t>
-  </si>
-  <si>
-    <t>BCH16 (Sa_1&amp;Sa_2 = 0 for RSN = 5663</t>
-  </si>
-  <si>
-    <t>7 RSNs newly added after removing 5663</t>
   </si>
   <si>
     <t xml:space="preserve"> Magnitude</t>
@@ -326,15 +125,57 @@
   <si>
     <t>unscaled spectra, PGA (g)</t>
   </si>
+  <si>
+    <t>UnscaledAccRecord6262</t>
+  </si>
+  <si>
+    <t>UnscaledAccRecord6263</t>
+  </si>
+  <si>
+    <t>UnscaledAccRecord6283</t>
+  </si>
+  <si>
+    <t>8 RSNs newly added</t>
+  </si>
+  <si>
+    <t>Duration Before Trim</t>
+  </si>
+  <si>
+    <t>Duration After 5% Trim</t>
+  </si>
+  <si>
+    <t>EQID</t>
+  </si>
+  <si>
+    <t>% Reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCH16 </t>
+  </si>
+  <si>
+    <t>(UnscaledAccRecord4673)</t>
+  </si>
+  <si>
+    <t>BCH16 (Sa_1&amp;Sa_2 = 0 for RSN = 5663,)</t>
+  </si>
+  <si>
+    <t>Avg</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>TotalDuration</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,8 +219,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,8 +260,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -458,21 +326,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -481,6 +363,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="4" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="4" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -493,16 +403,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="2" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -515,6 +420,1856 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1076676137132343"/>
+          <c:y val="0.11501737958430872"/>
+          <c:w val="0.82992688800497871"/>
+          <c:h val="0.77769017957994335"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>BCH16</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'GMSel_ΔM (±)'!$I$39:$I$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>70011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>70012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70021</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70031</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70032</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70041</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70042</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70051</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>70052</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>70061</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>70062</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>70071</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70072</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>70081</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>70082</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>70091</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>70092</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70101</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>70102</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>70111</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>70112</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>70121</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>70122</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>70131</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>70132</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>70141</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>70142</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>70151</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>70152</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>70161</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>70162</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>70171</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>70172</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>70181</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>70182</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>70191</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>70192</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>70201</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>70202</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>70211</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>70212</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>70221</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>70222</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>70231</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>70232</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>70241</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>70242</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>70251</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>70252</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>70261</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>70262</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>70271</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>70272</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>70281</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>70282</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>70291</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>70292</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>70301</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>70302</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'GMSel_ΔM (±)'!$L$39:$L$98</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31111111111111112</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.63492063492063489</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.61904761904761907</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.27777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.27777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.3333333333333338E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.21590909090909091</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.26923076923076922</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.32051282051282054</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.3333333333333333E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.37777777777777777</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.3888888888888889</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.43333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.41111111111111109</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.72222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.27777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.4777777777777778</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.35555555555555557</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.2890625</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.3203125</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.18888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.18888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.31111111111111112</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.32222222222222224</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.73394495412844041</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.30275229357798167</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.56666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.53086419753086422</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.44444444444444442</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.61250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.52500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.54651162790697672</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.37209302325581395</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6.8965517241379309E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.10714285714285714</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.5714285714285712E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.44897959183673469</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.59183673469387754</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.27272727272727271</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.21212121212121213</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.32500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.22500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.1206896551724138</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.27586206896551724</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9D4D-41FF-B14B-99C1DEC83C8A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>CY14</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'GMSel_ΔM (±)'!$N$39:$N$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'GMSel_ΔM (±)'!$Q$39:$Q$98</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="60"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9D4D-41FF-B14B-99C1DEC83C8A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>ASK14</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'GMSel_ΔM (±)'!$S$39:$S$98</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>70011</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>70012</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70021</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70031</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70032</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70041</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70042</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70051</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>70052</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>70061</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>70062</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>70071</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70072</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>70081</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>70082</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>70091</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>70092</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70101</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>70102</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>70111</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>70112</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>70121</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>70122</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>70131</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>70132</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>70141</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>70142</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>70151</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>70152</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>70161</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>70162</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>70171</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>70172</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>70181</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>70182</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>70191</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>70192</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>70201</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>70202</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>70211</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>70212</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>70221</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>70222</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>70231</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>70232</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>70241</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>70242</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>70251</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>70252</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>70261</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>70262</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>70271</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>70272</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>70281</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>70282</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>70291</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>70292</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>70301</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>70302</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'GMSel_ΔM (±)'!$V$39:$V$98</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28409090909090912</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28409090909090912</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.3333333333333338E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.21590909090909091</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.26923076923076922</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.32051282051282054</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27966101694915252</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.3559322033898305</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.42222222222222222</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.42222222222222222</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.22222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.31111111111111112</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.3333333333333333E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.24444444444444444</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.28888888888888886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.37777777777777777</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.26666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.32222222222222224</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.27777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.32222222222222224</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.32222222222222224</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.4777777777777778</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.24444444444444444</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.35555555555555557</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.35555555555555557</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.2890625</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.3203125</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.18888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.18888888888888888</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.31111111111111112</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.32222222222222224</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.5679012345679012</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.65432098765432101</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.74683544303797467</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.46835443037974683</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.54651162790697672</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.37209302325581395</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6.8965517241379309E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.27272727272727271</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.21212121212121213</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.32500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.22500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.41666666666666669</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.36666666666666664</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.6923076923076927E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.128205128205128E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.1206896551724138</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.27586206896551724</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9D4D-41FF-B14B-99C1DEC83C8A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="890227680"/>
+        <c:axId val="685713072"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="890227680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>EQID</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="685713072"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="685713072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IN" sz="1200" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>% Reduction</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="890227680"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>523874</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4FA6E8F-E41D-793F-1544-61480892882D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -780,117 +2535,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X99"/>
+  <dimension ref="A1:AL103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="24" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="13" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="26.5703125" customWidth="1"/>
+    <col min="11" max="12" width="24.5703125" customWidth="1"/>
+    <col min="13" max="13" width="25" customWidth="1"/>
+    <col min="14" max="14" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.85546875" customWidth="1"/>
+    <col min="16" max="16" width="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" customWidth="1"/>
+    <col min="18" max="18" width="22.42578125" customWidth="1"/>
+    <col min="19" max="19" width="24.7109375" customWidth="1"/>
+    <col min="20" max="20" width="22.7109375" customWidth="1"/>
+    <col min="21" max="21" width="25" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="I1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="M1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="R1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
+    <row r="1" spans="1:25" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="I1" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="S1" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-      <c r="I2" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="12"/>
-      <c r="M2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="N2" s="11"/>
-      <c r="O2" s="12"/>
-      <c r="R2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="S2" s="11"/>
-      <c r="T2" s="12"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
+      <c r="I2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="19"/>
+      <c r="P2" s="20"/>
+      <c r="S2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="T2" s="19"/>
+      <c r="U2" s="20"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" ht="21" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -913,34 +2691,36 @@
         <v>1</v>
       </c>
       <c r="J4" s="1">
+        <v>1575</v>
+      </c>
+      <c r="K4" s="1">
+        <v>4.0995999999999997</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
         <v>1524</v>
       </c>
-      <c r="K4" s="1">
+      <c r="P4" s="1">
         <v>4.7487000000000004</v>
       </c>
-      <c r="M4" s="1">
+      <c r="S4" s="1">
         <v>1</v>
       </c>
-      <c r="N4" s="1">
+      <c r="T4" s="1">
         <v>1524</v>
       </c>
-      <c r="O4" s="1">
+      <c r="U4" s="1">
         <v>4.7487000000000004</v>
       </c>
-      <c r="R4" s="1">
-        <v>1</v>
-      </c>
-      <c r="S4" s="1">
-        <v>1524</v>
-      </c>
-      <c r="T4" s="1">
-        <v>4.7487000000000004</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -963,34 +2743,36 @@
         <v>2</v>
       </c>
       <c r="J5" s="1">
-        <v>4891</v>
+        <v>1524</v>
       </c>
       <c r="K5" s="1">
-        <v>3.794</v>
-      </c>
-      <c r="M5" s="1">
+        <v>4.7487000000000004</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1">
         <v>2</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>1472</v>
       </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1">
         <v>2.7484000000000002</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>2</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <v>1575</v>
       </c>
-      <c r="T5" s="1">
+      <c r="U5" s="1">
         <v>4.0995999999999997</v>
       </c>
-      <c r="X5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -1018,26 +2800,28 @@
       <c r="K6" s="1">
         <v>4.5038999999999998</v>
       </c>
-      <c r="M6" s="1">
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1">
         <v>3</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>1469</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>4.2964000000000002</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>3</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <v>1436</v>
       </c>
-      <c r="T6" s="1">
+      <c r="U6" s="1">
         <v>3.3534999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -1050,7 +2834,7 @@
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>5663</v>
       </c>
       <c r="G7" s="1">
@@ -1065,30 +2849,32 @@
       <c r="K7" s="1">
         <v>3.6293000000000002</v>
       </c>
-      <c r="M7" s="1">
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1">
         <v>4</v>
       </c>
-      <c r="N7" s="7">
+      <c r="O7" s="5">
         <v>4884</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>3.6293000000000002</v>
       </c>
-      <c r="R7" s="1">
+      <c r="S7" s="1">
         <v>4</v>
       </c>
-      <c r="S7" s="7">
+      <c r="T7" s="5">
         <v>4884</v>
       </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
         <v>3.6293000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>5663</v>
       </c>
       <c r="C8" s="1">
@@ -1107,31 +2893,33 @@
         <v>5</v>
       </c>
       <c r="J8" s="1">
-        <v>1484</v>
+        <v>3281</v>
       </c>
       <c r="K8" s="1">
-        <v>3.8065000000000002</v>
-      </c>
-      <c r="M8" s="1">
+        <v>4.5603999999999996</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1">
         <v>5</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>1436</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>3.3534999999999999</v>
       </c>
-      <c r="R8" s="1">
+      <c r="S8" s="1">
         <v>5</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <v>1472</v>
       </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
         <v>2.7484000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -1153,36 +2941,38 @@
       <c r="I9" s="1">
         <v>6</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="9">
+        <v>1522</v>
+      </c>
+      <c r="K9" s="1">
+        <v>3.8698000000000001</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1">
+        <v>6</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1166</v>
+      </c>
+      <c r="P9" s="1">
+        <v>2.7244999999999999</v>
+      </c>
+      <c r="S9" s="1">
+        <v>6</v>
+      </c>
+      <c r="T9" s="1">
         <v>1469</v>
       </c>
-      <c r="K9" s="1">
+      <c r="U9" s="1">
         <v>4.2964000000000002</v>
       </c>
-      <c r="M9" s="1">
-        <v>6</v>
-      </c>
-      <c r="N9" s="1">
-        <v>1166</v>
-      </c>
-      <c r="O9" s="1">
-        <v>2.7244999999999999</v>
-      </c>
-      <c r="R9" s="1">
-        <v>6</v>
-      </c>
-      <c r="S9" s="1">
-        <v>1469</v>
-      </c>
-      <c r="T9" s="1">
-        <v>4.2964000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>1557</v>
       </c>
       <c r="C10" s="1">
@@ -1191,7 +2981,7 @@
       <c r="E10" s="1">
         <v>7</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>1557</v>
       </c>
       <c r="G10" s="1">
@@ -1201,31 +2991,33 @@
         <v>7</v>
       </c>
       <c r="J10" s="1">
-        <v>963</v>
+        <v>1166</v>
       </c>
       <c r="K10" s="1">
-        <v>1.8362000000000001</v>
-      </c>
-      <c r="M10" s="1">
+        <v>2.7244999999999999</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1">
         <v>7</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>1525</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>4.9107000000000003</v>
       </c>
-      <c r="R10" s="1">
+      <c r="S10" s="1">
         <v>7</v>
       </c>
-      <c r="S10" s="1">
+      <c r="T10" s="1">
         <v>3307</v>
       </c>
-      <c r="T10" s="1">
+      <c r="U10" s="1">
         <v>4.5038999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -1248,31 +3040,33 @@
         <v>8</v>
       </c>
       <c r="J11" s="1">
-        <v>3751</v>
+        <v>1286</v>
       </c>
       <c r="K11" s="1">
-        <v>3.5095999999999998</v>
-      </c>
-      <c r="M11" s="1">
+        <v>3.7660999999999998</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1">
         <v>8</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <v>1522</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>3.8698000000000001</v>
       </c>
-      <c r="R11" s="1">
+      <c r="S11" s="1">
         <v>8</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <v>1470</v>
       </c>
-      <c r="T11" s="1">
+      <c r="U11" s="1">
         <v>4.4584999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -1295,31 +3089,33 @@
         <v>9</v>
       </c>
       <c r="J12" s="1">
-        <v>1292</v>
+        <v>1581</v>
       </c>
       <c r="K12" s="1">
-        <v>4.7225000000000001</v>
-      </c>
-      <c r="M12" s="1">
+        <v>3.3037999999999998</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1">
         <v>9</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>1455</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>4.0294999999999996</v>
       </c>
-      <c r="R12" s="1">
+      <c r="S12" s="1">
         <v>9</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <v>78</v>
       </c>
-      <c r="T12" s="1">
+      <c r="U12" s="1">
         <v>4.4333</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -1342,31 +3138,33 @@
         <v>10</v>
       </c>
       <c r="J13" s="1">
-        <v>1575</v>
+        <v>1469</v>
       </c>
       <c r="K13" s="1">
-        <v>4.0995999999999997</v>
-      </c>
-      <c r="M13" s="1">
+        <v>4.2964000000000002</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1">
         <v>10</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>1465</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>4.2470999999999997</v>
       </c>
-      <c r="R13" s="1">
+      <c r="S13" s="1">
         <v>10</v>
       </c>
-      <c r="S13" s="1">
+      <c r="T13" s="1">
         <v>1460</v>
       </c>
-      <c r="T13" s="1">
+      <c r="U13" s="1">
         <v>4.5625999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -1389,31 +3187,33 @@
         <v>11</v>
       </c>
       <c r="J14" s="1">
-        <v>1581</v>
+        <v>1555</v>
       </c>
       <c r="K14" s="1">
-        <v>3.3037999999999998</v>
-      </c>
-      <c r="M14" s="1">
+        <v>3.1690999999999998</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1">
         <v>11</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>1575</v>
       </c>
-      <c r="O14" s="1">
+      <c r="P14" s="1">
         <v>4.0995999999999997</v>
       </c>
-      <c r="R14" s="1">
+      <c r="S14" s="1">
         <v>11</v>
       </c>
-      <c r="S14" s="7">
+      <c r="T14" s="5">
         <v>1557</v>
       </c>
-      <c r="T14" s="1">
+      <c r="U14" s="1">
         <v>4.702</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -1436,31 +3236,33 @@
         <v>12</v>
       </c>
       <c r="J15" s="1">
-        <v>78</v>
+        <v>3751</v>
       </c>
       <c r="K15" s="1">
-        <v>4.4333</v>
-      </c>
-      <c r="M15" s="1">
+        <v>3.5095999999999998</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1">
         <v>12</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <v>4350</v>
       </c>
-      <c r="O15" s="1">
+      <c r="P15" s="1">
         <v>3.1278000000000001</v>
       </c>
-      <c r="R15" s="1">
+      <c r="S15" s="1">
         <v>12</v>
       </c>
-      <c r="S15" s="1">
+      <c r="T15" s="1">
         <v>1514</v>
       </c>
-      <c r="T15" s="1">
+      <c r="U15" s="1">
         <v>3.9205999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -1483,31 +3285,33 @@
         <v>13</v>
       </c>
       <c r="J16" s="1">
-        <v>1436</v>
+        <v>1557</v>
       </c>
       <c r="K16" s="1">
-        <v>3.3534999999999999</v>
-      </c>
-      <c r="M16" s="1">
+        <v>4.702</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1">
         <v>13</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <v>1470</v>
       </c>
-      <c r="O16" s="1">
+      <c r="P16" s="1">
         <v>4.4584999999999999</v>
       </c>
-      <c r="R16" s="1">
+      <c r="S16" s="1">
         <v>13</v>
       </c>
-      <c r="S16" s="1">
+      <c r="T16" s="1">
         <v>5778</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <v>4.0232000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -1530,31 +3334,33 @@
         <v>14</v>
       </c>
       <c r="J17" s="1">
+        <v>1436</v>
+      </c>
+      <c r="K17" s="1">
+        <v>3.3534999999999999</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1">
         <v>14</v>
       </c>
-      <c r="K17" s="1">
-        <v>4.2011000000000003</v>
-      </c>
-      <c r="M17" s="1">
+      <c r="O17" s="1">
+        <v>3307</v>
+      </c>
+      <c r="P17" s="1">
+        <v>4.5038999999999998</v>
+      </c>
+      <c r="S17" s="1">
         <v>14</v>
       </c>
-      <c r="N17" s="1">
-        <v>3307</v>
-      </c>
-      <c r="O17" s="1">
-        <v>4.5038999999999998</v>
-      </c>
-      <c r="R17" s="1">
-        <v>14</v>
-      </c>
-      <c r="S17" s="1">
+      <c r="T17" s="1">
         <v>1581</v>
       </c>
-      <c r="T17" s="1">
+      <c r="U17" s="1">
         <v>3.3037999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -1577,31 +3383,33 @@
         <v>15</v>
       </c>
       <c r="J18" s="1">
-        <v>3865</v>
+        <v>1485</v>
       </c>
       <c r="K18" s="1">
-        <v>4.3784000000000001</v>
-      </c>
-      <c r="M18" s="1">
+        <v>4.1379000000000001</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1">
         <v>15</v>
       </c>
-      <c r="N18" s="1">
+      <c r="O18" s="1">
         <v>1581</v>
       </c>
-      <c r="O18" s="1">
+      <c r="P18" s="1">
         <v>3.3037999999999998</v>
       </c>
-      <c r="R18" s="1">
+      <c r="S18" s="1">
         <v>15</v>
       </c>
-      <c r="S18" s="1">
+      <c r="T18" s="1">
         <v>1455</v>
       </c>
-      <c r="T18" s="1">
+      <c r="U18" s="1">
         <v>4.0294999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1624,31 +3432,33 @@
         <v>16</v>
       </c>
       <c r="J19" s="1">
-        <v>1557</v>
+        <v>1292</v>
       </c>
       <c r="K19" s="1">
-        <v>4.702</v>
-      </c>
-      <c r="M19" s="1">
+        <v>4.7225000000000001</v>
+      </c>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1">
         <v>16</v>
       </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
         <v>1263</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <v>4.3055000000000003</v>
       </c>
-      <c r="R19" s="1">
+      <c r="S19" s="1">
         <v>16</v>
       </c>
-      <c r="S19" s="1">
+      <c r="T19" s="1">
         <v>4350</v>
       </c>
-      <c r="T19" s="1">
+      <c r="U19" s="1">
         <v>3.1278000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1671,31 +3481,33 @@
         <v>17</v>
       </c>
       <c r="J20" s="1">
+        <v>78</v>
+      </c>
+      <c r="K20" s="1">
+        <v>4.4333</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1">
+        <v>17</v>
+      </c>
+      <c r="O20" s="1">
         <v>3750</v>
       </c>
-      <c r="K20" s="1">
+      <c r="P20" s="1">
         <v>2.2536999999999998</v>
       </c>
-      <c r="M20" s="1">
+      <c r="S20" s="1">
         <v>17</v>
       </c>
-      <c r="N20" s="1">
-        <v>3750</v>
-      </c>
-      <c r="O20" s="1">
-        <v>2.2536999999999998</v>
-      </c>
-      <c r="R20" s="1">
-        <v>17</v>
-      </c>
-      <c r="S20" s="1">
+      <c r="T20" s="1">
         <v>1166</v>
       </c>
-      <c r="T20" s="1">
+      <c r="U20" s="1">
         <v>2.7244999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -1717,36 +3529,38 @@
       <c r="I21" s="1">
         <v>18</v>
       </c>
-      <c r="J21" s="1">
-        <v>1166</v>
+      <c r="J21" s="9">
+        <v>1484</v>
       </c>
       <c r="K21" s="1">
-        <v>2.7244999999999999</v>
-      </c>
-      <c r="M21" s="1">
+        <v>3.8065000000000002</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1">
         <v>18</v>
       </c>
-      <c r="N21" s="1">
+      <c r="O21" s="1">
         <v>78</v>
       </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
         <v>4.4333</v>
       </c>
-      <c r="R21" s="1">
+      <c r="S21" s="1">
         <v>18</v>
       </c>
-      <c r="S21" s="1">
+      <c r="T21" s="1">
         <v>1465</v>
       </c>
-      <c r="T21" s="1">
+      <c r="U21" s="1">
         <v>4.2470999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>19</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="5">
         <v>4884</v>
       </c>
       <c r="C22" s="1">
@@ -1765,31 +3579,33 @@
         <v>19</v>
       </c>
       <c r="J22" s="1">
-        <v>4350</v>
+        <v>14</v>
       </c>
       <c r="K22" s="1">
-        <v>3.1278000000000001</v>
-      </c>
-      <c r="M22" s="1">
+        <v>4.2011000000000003</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1">
         <v>19</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <v>736</v>
       </c>
-      <c r="O22" s="1">
+      <c r="P22" s="1">
         <v>3.79</v>
       </c>
-      <c r="R22" s="1">
+      <c r="S22" s="1">
         <v>19</v>
       </c>
-      <c r="S22" s="1">
+      <c r="T22" s="1">
         <v>1263</v>
       </c>
-      <c r="T22" s="1">
+      <c r="U22" s="1">
         <v>4.3055000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -1817,26 +3633,28 @@
       <c r="K23" s="1">
         <v>4.0869999999999997</v>
       </c>
-      <c r="M23" s="1">
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1">
         <v>20</v>
       </c>
-      <c r="N23" s="1">
+      <c r="O23" s="1">
         <v>5778</v>
       </c>
-      <c r="O23" s="1">
+      <c r="P23" s="1">
         <v>4.0232000000000001</v>
       </c>
-      <c r="R23" s="1">
+      <c r="S23" s="1">
         <v>20</v>
       </c>
-      <c r="S23" s="1">
+      <c r="T23" s="1">
         <v>1523</v>
       </c>
-      <c r="T23" s="1">
+      <c r="U23" s="1">
         <v>3.9708999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -1858,32 +3676,34 @@
       <c r="I24" s="1">
         <v>21</v>
       </c>
-      <c r="J24" s="1">
-        <v>6980</v>
+      <c r="J24" s="9">
+        <v>2661</v>
       </c>
       <c r="K24" s="1">
-        <v>4.9307999999999996</v>
-      </c>
-      <c r="M24" s="1">
+        <v>3.4771999999999998</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1">
         <v>21</v>
       </c>
-      <c r="N24" s="1">
+      <c r="O24" s="1">
         <v>14</v>
       </c>
-      <c r="O24" s="1">
+      <c r="P24" s="1">
         <v>4.2011000000000003</v>
       </c>
-      <c r="R24" s="1">
+      <c r="S24" s="1">
         <v>21</v>
       </c>
-      <c r="S24" s="1">
+      <c r="T24" s="1">
         <v>1453</v>
       </c>
-      <c r="T24" s="1">
+      <c r="U24" s="1">
         <v>4.6933999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -1896,7 +3716,7 @@
       <c r="E25" s="1">
         <v>22</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="5">
         <v>4884</v>
       </c>
       <c r="G25" s="1">
@@ -1905,32 +3725,34 @@
       <c r="I25" s="1">
         <v>22</v>
       </c>
-      <c r="J25" s="1">
-        <v>3281</v>
+      <c r="J25" s="9">
+        <v>4891</v>
       </c>
       <c r="K25" s="1">
-        <v>4.5603999999999996</v>
-      </c>
-      <c r="M25" s="1">
+        <v>3.794</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1">
         <v>22</v>
       </c>
-      <c r="N25" s="1">
+      <c r="O25" s="1">
         <v>2661</v>
       </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
         <v>3.4771999999999998</v>
       </c>
-      <c r="R25" s="1">
+      <c r="S25" s="1">
         <v>22</v>
       </c>
-      <c r="S25" s="1">
+      <c r="T25" s="1">
         <v>2650</v>
       </c>
-      <c r="T25" s="1">
+      <c r="U25" s="1">
         <v>3.3233000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -1953,31 +3775,33 @@
         <v>23</v>
       </c>
       <c r="J26" s="1">
-        <v>1453</v>
+        <v>3750</v>
       </c>
       <c r="K26" s="1">
-        <v>4.6933999999999996</v>
-      </c>
-      <c r="M26" s="1">
+        <v>2.2536999999999998</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1">
         <v>23</v>
       </c>
-      <c r="N26" s="1">
+      <c r="O26" s="1">
         <v>1292</v>
       </c>
-      <c r="O26" s="1">
+      <c r="P26" s="1">
         <v>4.7225000000000001</v>
       </c>
-      <c r="R26" s="1">
+      <c r="S26" s="1">
         <v>23</v>
       </c>
-      <c r="S26" s="1">
+      <c r="T26" s="1">
         <v>3750</v>
       </c>
-      <c r="T26" s="1">
+      <c r="U26" s="1">
         <v>2.2536999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -1999,32 +3823,34 @@
       <c r="I27" s="1">
         <v>24</v>
       </c>
-      <c r="J27" s="1">
-        <v>1286</v>
+      <c r="J27" s="9">
+        <v>1453</v>
       </c>
       <c r="K27" s="1">
-        <v>3.7660999999999998</v>
-      </c>
-      <c r="M27" s="1">
+        <v>4.6933999999999996</v>
+      </c>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1">
         <v>24</v>
       </c>
-      <c r="N27" s="1">
+      <c r="O27" s="1">
         <v>1453</v>
       </c>
-      <c r="O27" s="1">
+      <c r="P27" s="1">
         <v>4.6933999999999996</v>
       </c>
-      <c r="R27" s="1">
+      <c r="S27" s="1">
         <v>24</v>
       </c>
-      <c r="S27" s="1">
+      <c r="T27" s="1">
         <v>3269</v>
       </c>
-      <c r="T27" s="1">
+      <c r="U27" s="1">
         <v>4.3053999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -2047,31 +3873,33 @@
         <v>25</v>
       </c>
       <c r="J28" s="1">
-        <v>2466</v>
+        <v>1478</v>
       </c>
       <c r="K28" s="1">
-        <v>4.3760000000000003</v>
-      </c>
-      <c r="M28" s="1">
+        <v>2.8592</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1">
         <v>25</v>
       </c>
-      <c r="N28" s="1">
+      <c r="O28" s="1">
         <v>3281</v>
       </c>
-      <c r="O28" s="1">
+      <c r="P28" s="1">
         <v>4.5603999999999996</v>
       </c>
-      <c r="R28" s="1">
+      <c r="S28" s="1">
         <v>25</v>
       </c>
-      <c r="S28" s="1">
+      <c r="T28" s="1">
         <v>1522</v>
       </c>
-      <c r="T28" s="1">
+      <c r="U28" s="1">
         <v>3.8698000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -2093,32 +3921,34 @@
       <c r="I29" s="1">
         <v>26</v>
       </c>
-      <c r="J29" s="1">
-        <v>1472</v>
+      <c r="J29" s="9">
+        <v>3264</v>
       </c>
       <c r="K29" s="1">
-        <v>2.7484000000000002</v>
-      </c>
-      <c r="M29" s="1">
+        <v>4.9166999999999996</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1">
         <v>26</v>
       </c>
-      <c r="N29" s="7">
+      <c r="O29" s="5">
         <v>1557</v>
       </c>
-      <c r="O29" s="1">
+      <c r="P29" s="1">
         <v>4.702</v>
       </c>
-      <c r="R29" s="1">
+      <c r="S29" s="1">
         <v>26</v>
       </c>
-      <c r="S29" s="1">
+      <c r="T29" s="1">
         <v>1555</v>
       </c>
-      <c r="T29" s="1">
+      <c r="U29" s="1">
         <v>3.1690999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -2141,31 +3971,33 @@
         <v>27</v>
       </c>
       <c r="J30" s="1">
-        <v>1269</v>
+        <v>4350</v>
       </c>
       <c r="K30" s="1">
-        <v>3.6257999999999999</v>
-      </c>
-      <c r="M30" s="1">
+        <v>3.1278000000000001</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1">
         <v>27</v>
       </c>
-      <c r="N30" s="1">
+      <c r="O30" s="1">
         <v>1555</v>
       </c>
-      <c r="O30" s="1">
+      <c r="P30" s="1">
         <v>3.1690999999999998</v>
       </c>
-      <c r="R30" s="1">
+      <c r="S30" s="1">
         <v>27</v>
       </c>
-      <c r="S30" s="1">
+      <c r="T30" s="1">
         <v>14</v>
       </c>
-      <c r="T30" s="1">
+      <c r="U30" s="1">
         <v>4.2011000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2187,32 +4019,34 @@
       <c r="I31" s="1">
         <v>28</v>
       </c>
-      <c r="J31" s="1">
-        <v>3264</v>
+      <c r="J31" s="9">
+        <v>1295</v>
       </c>
       <c r="K31" s="1">
-        <v>4.9166999999999996</v>
-      </c>
-      <c r="M31" s="1">
+        <v>3.9836999999999998</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1">
         <v>28</v>
       </c>
-      <c r="N31" s="1">
+      <c r="O31" s="1">
         <v>1286</v>
       </c>
-      <c r="O31" s="1">
+      <c r="P31" s="1">
         <v>3.7660999999999998</v>
       </c>
-      <c r="R31" s="1">
+      <c r="S31" s="1">
         <v>28</v>
       </c>
-      <c r="S31" s="1">
+      <c r="T31" s="1">
         <v>3281</v>
       </c>
-      <c r="T31" s="1">
+      <c r="U31" s="1">
         <v>4.5603999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -2234,32 +4068,34 @@
       <c r="I32" s="1">
         <v>29</v>
       </c>
-      <c r="J32" s="1">
-        <v>1555</v>
+      <c r="J32" s="9">
+        <v>3865</v>
       </c>
       <c r="K32" s="1">
-        <v>3.1690999999999998</v>
-      </c>
-      <c r="M32" s="1">
+        <v>4.3784000000000001</v>
+      </c>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1">
         <v>29</v>
       </c>
-      <c r="N32" s="1">
+      <c r="O32" s="1">
         <v>1460</v>
       </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
         <v>4.5625999999999998</v>
       </c>
-      <c r="R32" s="1">
+      <c r="S32" s="1">
         <v>29</v>
       </c>
-      <c r="S32" s="1">
+      <c r="T32" s="1">
         <v>736</v>
       </c>
-      <c r="T32" s="1">
+      <c r="U32" s="1">
         <v>3.79</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2283,556 +4119,2502 @@
         <v>30</v>
       </c>
       <c r="J33" s="1">
-        <v>1465</v>
+        <v>2466</v>
       </c>
       <c r="K33" s="1">
-        <v>4.2470999999999997</v>
-      </c>
-      <c r="M33" s="1">
+        <v>4.3760000000000003</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1">
         <v>30</v>
       </c>
-      <c r="N33" s="1">
+      <c r="O33" s="1">
         <v>1523</v>
       </c>
-      <c r="O33" s="1">
+      <c r="P33" s="1">
         <v>3.9708999999999999</v>
       </c>
-      <c r="R33" s="1">
+      <c r="S33" s="1">
         <v>30</v>
       </c>
-      <c r="S33" s="1">
+      <c r="T33" s="1">
         <v>1525</v>
       </c>
-      <c r="T33" s="1">
+      <c r="U33" s="1">
         <v>4.9107000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I35" t="s">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="B35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="J36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="I38" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N38" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="O38" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="P38" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q38" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="S38" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T38" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="U38" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="V38" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="11"/>
+      <c r="I39" s="1">
+        <v>70011</v>
+      </c>
+      <c r="J39" s="1">
+        <v>30</v>
+      </c>
+      <c r="K39" s="1">
+        <v>30</v>
+      </c>
+      <c r="L39" s="11">
+        <f>(J39-K39)/J39</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="11"/>
+      <c r="S39" s="1">
+        <v>70011</v>
+      </c>
+      <c r="T39" s="1">
+        <v>30</v>
+      </c>
+      <c r="U39" s="1">
+        <v>30</v>
+      </c>
+      <c r="V39" s="11">
+        <f>(T39-U39)/T39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="11"/>
+      <c r="I40" s="1">
+        <v>70012</v>
+      </c>
+      <c r="J40" s="1">
+        <v>30</v>
+      </c>
+      <c r="K40" s="1">
+        <v>30</v>
+      </c>
+      <c r="L40" s="11">
+        <f t="shared" ref="L40:L98" si="0">(J40-K40)/J40</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="11"/>
+      <c r="S40" s="1">
+        <v>70012</v>
+      </c>
+      <c r="T40" s="1">
+        <v>30</v>
+      </c>
+      <c r="U40" s="1">
+        <v>30</v>
+      </c>
+      <c r="V40" s="11">
+        <f t="shared" ref="V40:V98" si="1">(T40-U40)/T40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="11"/>
+      <c r="I41" s="1">
+        <v>70021</v>
+      </c>
+      <c r="J41" s="1">
+        <v>90</v>
+      </c>
+      <c r="K41" s="1">
+        <v>63</v>
+      </c>
+      <c r="L41" s="11">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="11"/>
+      <c r="S41" s="1">
+        <v>70021</v>
+      </c>
+      <c r="T41" s="1">
+        <v>88</v>
+      </c>
+      <c r="U41" s="1">
+        <v>63</v>
+      </c>
+      <c r="V41" s="11">
+        <f t="shared" si="1"/>
+        <v>0.28409090909090912</v>
+      </c>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="11"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1">
+        <v>70022</v>
+      </c>
+      <c r="J42" s="1">
+        <v>90</v>
+      </c>
+      <c r="K42" s="1">
+        <v>62</v>
+      </c>
+      <c r="L42" s="11">
+        <f t="shared" si="0"/>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1">
+        <v>70022</v>
+      </c>
+      <c r="T42" s="1">
+        <v>88</v>
+      </c>
+      <c r="U42" s="1">
+        <v>63</v>
+      </c>
+      <c r="V42" s="11">
+        <f t="shared" si="1"/>
+        <v>0.28409090909090912</v>
+      </c>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AH42" s="1"/>
+      <c r="AI42" s="1"/>
+      <c r="AJ42" s="1"/>
+      <c r="AK42" s="1"/>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="11"/>
+      <c r="I43" s="1">
+        <v>70031</v>
+      </c>
+      <c r="J43" s="1">
+        <v>126</v>
+      </c>
+      <c r="K43" s="1">
+        <v>46</v>
+      </c>
+      <c r="L43" s="11">
+        <f t="shared" si="0"/>
+        <v>0.63492063492063489</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="11"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1">
+        <v>70031</v>
+      </c>
+      <c r="T43" s="1">
+        <v>75</v>
+      </c>
+      <c r="U43" s="1">
+        <v>68</v>
+      </c>
+      <c r="V43" s="11">
+        <f t="shared" si="1"/>
+        <v>9.3333333333333338E-2</v>
+      </c>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AH43" s="1"/>
+      <c r="AI43" s="1"/>
+      <c r="AJ43" s="1"/>
+      <c r="AK43" s="1"/>
+      <c r="AL43" s="1"/>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="11"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1">
+        <v>70032</v>
+      </c>
+      <c r="J44" s="1">
+        <v>126</v>
+      </c>
+      <c r="K44" s="1">
+        <v>48</v>
+      </c>
+      <c r="L44" s="11">
+        <f t="shared" si="0"/>
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="11"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1">
+        <v>70032</v>
+      </c>
+      <c r="T44" s="1">
+        <v>75</v>
+      </c>
+      <c r="U44" s="1">
+        <v>69</v>
+      </c>
+      <c r="V44" s="11">
+        <f t="shared" si="1"/>
+        <v>0.08</v>
+      </c>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="11"/>
+      <c r="I45" s="1">
+        <v>70041</v>
+      </c>
+      <c r="J45" s="1">
+        <v>90</v>
+      </c>
+      <c r="K45" s="1">
+        <v>65</v>
+      </c>
+      <c r="L45" s="11">
+        <f t="shared" si="0"/>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="11"/>
+      <c r="S45" s="1">
+        <v>70041</v>
+      </c>
+      <c r="T45" s="1">
+        <v>88</v>
+      </c>
+      <c r="U45" s="1">
+        <v>69</v>
+      </c>
+      <c r="V45" s="11">
+        <f t="shared" si="1"/>
+        <v>0.21590909090909091</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="11"/>
+      <c r="I46" s="1">
+        <v>70042</v>
+      </c>
+      <c r="J46" s="1">
+        <v>90</v>
+      </c>
+      <c r="K46" s="1">
+        <v>65</v>
+      </c>
+      <c r="L46" s="11">
+        <f t="shared" si="0"/>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="11"/>
+      <c r="S46" s="1">
+        <v>70042</v>
+      </c>
+      <c r="T46" s="1">
+        <v>88</v>
+      </c>
+      <c r="U46" s="1">
+        <v>55</v>
+      </c>
+      <c r="V46" s="11">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="11"/>
+      <c r="I47" s="1">
+        <v>70051</v>
+      </c>
+      <c r="J47" s="1">
+        <v>75</v>
+      </c>
+      <c r="K47" s="1">
+        <v>68</v>
+      </c>
+      <c r="L47" s="11">
+        <f t="shared" si="0"/>
+        <v>9.3333333333333338E-2</v>
+      </c>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="11"/>
+      <c r="S47" s="1">
+        <v>70051</v>
+      </c>
+      <c r="T47" s="1">
+        <v>78</v>
+      </c>
+      <c r="U47" s="1">
+        <v>57</v>
+      </c>
+      <c r="V47" s="11">
+        <f t="shared" si="1"/>
+        <v>0.26923076923076922</v>
+      </c>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="11"/>
+      <c r="I48" s="1">
+        <v>70052</v>
+      </c>
+      <c r="J48" s="1">
+        <v>75</v>
+      </c>
+      <c r="K48" s="1">
+        <v>69</v>
+      </c>
+      <c r="L48" s="11">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="11"/>
+      <c r="S48" s="1">
+        <v>70052</v>
+      </c>
+      <c r="T48" s="1">
+        <v>78</v>
+      </c>
+      <c r="U48" s="1">
+        <v>53</v>
+      </c>
+      <c r="V48" s="11">
+        <f t="shared" si="1"/>
+        <v>0.32051282051282054</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="11"/>
+      <c r="I49" s="1">
+        <v>70061</v>
+      </c>
+      <c r="J49" s="1">
+        <v>88</v>
+      </c>
+      <c r="K49" s="1">
+        <v>69</v>
+      </c>
+      <c r="L49" s="11">
+        <f t="shared" si="0"/>
+        <v>0.21590909090909091</v>
+      </c>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="11"/>
+      <c r="S49" s="1">
+        <v>70061</v>
+      </c>
+      <c r="T49" s="1">
+        <v>118</v>
+      </c>
+      <c r="U49" s="1">
+        <v>85</v>
+      </c>
+      <c r="V49" s="11">
+        <f t="shared" si="1"/>
+        <v>0.27966101694915252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="11"/>
+      <c r="I50" s="1">
+        <v>70062</v>
+      </c>
+      <c r="J50" s="1">
+        <v>88</v>
+      </c>
+      <c r="K50" s="1">
+        <v>55</v>
+      </c>
+      <c r="L50" s="11">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="11"/>
+      <c r="S50" s="1">
+        <v>70062</v>
+      </c>
+      <c r="T50" s="1">
+        <v>118</v>
+      </c>
+      <c r="U50" s="1">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="V50" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3559322033898305</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="11"/>
+      <c r="I51" s="1">
+        <v>70071</v>
+      </c>
+      <c r="J51" s="1">
+        <v>78</v>
+      </c>
+      <c r="K51" s="1">
+        <v>57</v>
+      </c>
+      <c r="L51" s="11">
+        <f t="shared" si="0"/>
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="11"/>
+      <c r="S51" s="1">
+        <v>70071</v>
+      </c>
+      <c r="T51" s="1">
+        <v>90</v>
+      </c>
+      <c r="U51" s="1">
+        <v>52</v>
+      </c>
+      <c r="V51" s="11">
+        <f t="shared" si="1"/>
+        <v>0.42222222222222222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="11"/>
+      <c r="I52" s="1">
+        <v>70072</v>
+      </c>
+      <c r="J52" s="1">
+        <v>78</v>
+      </c>
+      <c r="K52" s="1">
+        <v>53</v>
+      </c>
+      <c r="L52" s="11">
+        <f t="shared" si="0"/>
+        <v>0.32051282051282054</v>
+      </c>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="11"/>
+      <c r="S52" s="1">
+        <v>70072</v>
+      </c>
+      <c r="T52" s="1">
+        <v>90</v>
+      </c>
+      <c r="U52" s="1">
+        <v>52</v>
+      </c>
+      <c r="V52" s="11">
+        <f t="shared" si="1"/>
+        <v>0.42222222222222222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="11"/>
+      <c r="I53" s="1">
+        <v>70081</v>
+      </c>
+      <c r="J53" s="1">
+        <v>30</v>
+      </c>
+      <c r="K53" s="1">
+        <v>30</v>
+      </c>
+      <c r="L53" s="11">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="11"/>
+      <c r="S53" s="1">
+        <v>70081</v>
+      </c>
+      <c r="T53" s="1">
+        <v>90</v>
+      </c>
+      <c r="U53" s="1">
+        <v>70</v>
+      </c>
+      <c r="V53" s="11">
+        <f t="shared" si="1"/>
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="11"/>
+      <c r="I54" s="1">
+        <v>70082</v>
+      </c>
+      <c r="J54" s="1">
+        <v>30</v>
+      </c>
+      <c r="K54" s="1">
+        <v>29</v>
+      </c>
+      <c r="L54" s="11">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="11"/>
+      <c r="S54" s="1">
+        <v>70082</v>
+      </c>
+      <c r="T54" s="1">
+        <v>90</v>
+      </c>
+      <c r="U54" s="1">
+        <v>62</v>
+      </c>
+      <c r="V54" s="11">
+        <f t="shared" si="1"/>
+        <v>0.31111111111111112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="11"/>
+      <c r="I55" s="1">
+        <v>70091</v>
+      </c>
+      <c r="J55" s="1">
+        <v>90</v>
+      </c>
+      <c r="K55" s="1">
+        <v>56</v>
+      </c>
+      <c r="L55" s="11">
+        <f t="shared" si="0"/>
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="11"/>
+      <c r="S55" s="1">
+        <v>70091</v>
+      </c>
+      <c r="T55" s="1">
+        <v>30</v>
+      </c>
+      <c r="U55" s="1">
+        <v>30</v>
+      </c>
+      <c r="V55" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="11"/>
+      <c r="I56" s="1">
+        <v>70092</v>
+      </c>
+      <c r="J56" s="1">
+        <v>90</v>
+      </c>
+      <c r="K56" s="1">
+        <v>55</v>
+      </c>
+      <c r="L56" s="11">
+        <f t="shared" si="0"/>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="11"/>
+      <c r="S56" s="1">
+        <v>70092</v>
+      </c>
+      <c r="T56" s="1">
+        <v>30</v>
+      </c>
+      <c r="U56" s="1">
+        <v>29</v>
+      </c>
+      <c r="V56" s="11">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333333E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="11"/>
+      <c r="I57" s="1">
+        <v>70101</v>
+      </c>
+      <c r="J57" s="1">
+        <v>90</v>
+      </c>
+      <c r="K57" s="1">
+        <v>51</v>
+      </c>
+      <c r="L57" s="11">
+        <f t="shared" si="0"/>
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="11"/>
+      <c r="S57" s="1">
+        <v>70101</v>
+      </c>
+      <c r="T57" s="1">
+        <v>90</v>
+      </c>
+      <c r="U57" s="1">
+        <v>68</v>
+      </c>
+      <c r="V57" s="11">
+        <f t="shared" si="1"/>
+        <v>0.24444444444444444</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="11"/>
+      <c r="I58" s="1">
+        <v>70102</v>
+      </c>
+      <c r="J58" s="1">
+        <v>90</v>
+      </c>
+      <c r="K58" s="1">
+        <v>53</v>
+      </c>
+      <c r="L58" s="11">
+        <f t="shared" si="0"/>
+        <v>0.41111111111111109</v>
+      </c>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="11"/>
+      <c r="S58" s="1">
+        <v>70102</v>
+      </c>
+      <c r="T58" s="1">
+        <v>90</v>
+      </c>
+      <c r="U58" s="1">
+        <v>64</v>
+      </c>
+      <c r="V58" s="11">
+        <f t="shared" si="1"/>
+        <v>0.28888888888888886</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="11"/>
+      <c r="I59" s="1">
+        <v>70111</v>
+      </c>
+      <c r="J59" s="1">
+        <v>90</v>
+      </c>
+      <c r="K59" s="1">
+        <v>30</v>
+      </c>
+      <c r="L59" s="11">
+        <f t="shared" si="0"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="11"/>
+      <c r="S59" s="1">
+        <v>70111</v>
+      </c>
+      <c r="T59" s="1">
+        <v>90</v>
+      </c>
+      <c r="U59" s="1">
+        <v>60</v>
+      </c>
+      <c r="V59" s="11">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="11"/>
+      <c r="I60" s="1">
+        <v>70112</v>
+      </c>
+      <c r="J60" s="1">
+        <v>90</v>
+      </c>
+      <c r="K60" s="1">
+        <v>25</v>
+      </c>
+      <c r="L60" s="11">
+        <f t="shared" si="0"/>
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="11"/>
+      <c r="S60" s="1">
+        <v>70112</v>
+      </c>
+      <c r="T60" s="1">
+        <v>90</v>
+      </c>
+      <c r="U60" s="1">
+        <v>56</v>
+      </c>
+      <c r="V60" s="11">
+        <f t="shared" si="1"/>
+        <v>0.37777777777777777</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="11"/>
+      <c r="I61" s="1">
+        <v>70121</v>
+      </c>
+      <c r="J61" s="1">
+        <v>90</v>
+      </c>
+      <c r="K61" s="1">
+        <v>65</v>
+      </c>
+      <c r="L61" s="11">
+        <f t="shared" si="0"/>
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="11"/>
+      <c r="S61" s="1">
+        <v>70121</v>
+      </c>
+      <c r="T61" s="1">
+        <v>90</v>
+      </c>
+      <c r="U61" s="1">
+        <v>66</v>
+      </c>
+      <c r="V61" s="11">
+        <f t="shared" si="1"/>
+        <v>0.26666666666666666</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="11"/>
+      <c r="I62" s="1">
+        <v>70122</v>
+      </c>
+      <c r="J62" s="1">
+        <v>90</v>
+      </c>
+      <c r="K62" s="1">
         <v>63</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>2</v>
-      </c>
-      <c r="B41" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>5</v>
-      </c>
-      <c r="B44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>7</v>
-      </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>8</v>
-      </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>9</v>
-      </c>
-      <c r="B48" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>10</v>
-      </c>
-      <c r="B49" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>11</v>
-      </c>
-      <c r="B50" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>12</v>
-      </c>
-      <c r="B51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>13</v>
-      </c>
-      <c r="B52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>14</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>16</v>
-      </c>
-      <c r="B55" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>17</v>
-      </c>
-      <c r="B56" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>18</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="L62" s="11">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+      <c r="P62" s="1"/>
+      <c r="Q62" s="11"/>
+      <c r="S62" s="1">
+        <v>70122</v>
+      </c>
+      <c r="T62" s="1">
+        <v>90</v>
+      </c>
+      <c r="U62" s="1">
+        <v>61</v>
+      </c>
+      <c r="V62" s="11">
+        <f t="shared" si="1"/>
+        <v>0.32222222222222224</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="11"/>
+      <c r="I63" s="1">
+        <v>70131</v>
+      </c>
+      <c r="J63" s="1">
+        <v>90</v>
+      </c>
+      <c r="K63" s="1">
+        <v>47</v>
+      </c>
+      <c r="L63" s="11">
+        <f t="shared" si="0"/>
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="11"/>
+      <c r="S63" s="1">
+        <v>70131</v>
+      </c>
+      <c r="T63" s="1">
+        <v>90</v>
+      </c>
+      <c r="U63" s="1">
+        <v>65</v>
+      </c>
+      <c r="V63" s="11">
+        <f t="shared" si="1"/>
+        <v>0.27777777777777779</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="11"/>
+      <c r="I64" s="1">
+        <v>70132</v>
+      </c>
+      <c r="J64" s="1">
+        <v>90</v>
+      </c>
+      <c r="K64" s="1">
+        <v>30</v>
+      </c>
+      <c r="L64" s="11">
+        <f t="shared" si="0"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+      <c r="P64" s="1"/>
+      <c r="Q64" s="11"/>
+      <c r="S64" s="1">
+        <v>70132</v>
+      </c>
+      <c r="T64" s="1">
+        <v>90</v>
+      </c>
+      <c r="U64" s="1">
+        <v>63</v>
+      </c>
+      <c r="V64" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="11"/>
+      <c r="I65" s="1">
+        <v>70141</v>
+      </c>
+      <c r="J65" s="1">
+        <v>90</v>
+      </c>
+      <c r="K65" s="1">
+        <v>60</v>
+      </c>
+      <c r="L65" s="11">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="11"/>
+      <c r="S65" s="1">
+        <v>70141</v>
+      </c>
+      <c r="T65" s="1">
+        <v>90</v>
+      </c>
+      <c r="U65" s="1">
+        <v>61</v>
+      </c>
+      <c r="V65" s="11">
+        <f t="shared" si="1"/>
+        <v>0.32222222222222224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="11"/>
+      <c r="I66" s="1">
+        <v>70142</v>
+      </c>
+      <c r="J66" s="1">
+        <v>90</v>
+      </c>
+      <c r="K66" s="1">
+        <v>58</v>
+      </c>
+      <c r="L66" s="11">
+        <f t="shared" si="0"/>
+        <v>0.35555555555555557</v>
+      </c>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+      <c r="P66" s="1"/>
+      <c r="Q66" s="11"/>
+      <c r="S66" s="1">
+        <v>70142</v>
+      </c>
+      <c r="T66" s="1">
+        <v>90</v>
+      </c>
+      <c r="U66" s="1">
+        <v>61</v>
+      </c>
+      <c r="V66" s="11">
+        <f t="shared" si="1"/>
+        <v>0.32222222222222224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="11"/>
+      <c r="I67" s="1">
+        <v>70151</v>
+      </c>
+      <c r="J67" s="1">
+        <v>128</v>
+      </c>
+      <c r="K67" s="1">
+        <v>91</v>
+      </c>
+      <c r="L67" s="11">
+        <f t="shared" si="0"/>
+        <v>0.2890625</v>
+      </c>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+      <c r="P67" s="1"/>
+      <c r="Q67" s="11"/>
+      <c r="S67" s="1">
+        <v>70151</v>
+      </c>
+      <c r="T67" s="1">
+        <v>90</v>
+      </c>
+      <c r="U67" s="1">
+        <v>47</v>
+      </c>
+      <c r="V67" s="11">
+        <f t="shared" si="1"/>
+        <v>0.4777777777777778</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="11"/>
+      <c r="I68" s="1">
+        <v>70152</v>
+      </c>
+      <c r="J68" s="1">
+        <v>128</v>
+      </c>
+      <c r="K68" s="1">
+        <v>87</v>
+      </c>
+      <c r="L68" s="11">
+        <f t="shared" si="0"/>
+        <v>0.3203125</v>
+      </c>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="11"/>
+      <c r="S68" s="1">
+        <v>70152</v>
+      </c>
+      <c r="T68" s="1">
+        <v>90</v>
+      </c>
+      <c r="U68" s="1">
+        <v>30</v>
+      </c>
+      <c r="V68" s="11">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="11"/>
+      <c r="I69" s="1">
+        <v>70161</v>
+      </c>
+      <c r="J69" s="1">
+        <v>90</v>
+      </c>
+      <c r="K69" s="1">
+        <v>73</v>
+      </c>
+      <c r="L69" s="11">
+        <f t="shared" si="0"/>
+        <v>0.18888888888888888</v>
+      </c>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="11"/>
+      <c r="S69" s="1">
+        <v>70161</v>
+      </c>
+      <c r="T69" s="1">
+        <v>90</v>
+      </c>
+      <c r="U69" s="1">
+        <v>68</v>
+      </c>
+      <c r="V69" s="11">
+        <f t="shared" si="1"/>
+        <v>0.24444444444444444</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="11"/>
+      <c r="I70" s="1">
+        <v>70162</v>
+      </c>
+      <c r="J70" s="1">
+        <v>90</v>
+      </c>
+      <c r="K70" s="1">
+        <v>73</v>
+      </c>
+      <c r="L70" s="11">
+        <f t="shared" si="0"/>
+        <v>0.18888888888888888</v>
+      </c>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="12"/>
+      <c r="S70" s="1">
+        <v>70162</v>
+      </c>
+      <c r="T70" s="1">
+        <v>90</v>
+      </c>
+      <c r="U70" s="1">
+        <v>58</v>
+      </c>
+      <c r="V70" s="11">
+        <f t="shared" si="1"/>
+        <v>0.35555555555555557</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="11"/>
+      <c r="I71" s="1">
+        <v>70171</v>
+      </c>
+      <c r="J71" s="1">
+        <v>90</v>
+      </c>
+      <c r="K71" s="1">
+        <v>62</v>
+      </c>
+      <c r="L71" s="11">
+        <f t="shared" si="0"/>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+      <c r="P71" s="1"/>
+      <c r="Q71" s="11"/>
+      <c r="S71" s="1">
+        <v>70171</v>
+      </c>
+      <c r="T71" s="1">
+        <v>90</v>
+      </c>
+      <c r="U71" s="1">
+        <v>60</v>
+      </c>
+      <c r="V71" s="11">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="11"/>
+      <c r="I72" s="1">
+        <v>70172</v>
+      </c>
+      <c r="J72" s="1">
+        <v>90</v>
+      </c>
+      <c r="K72" s="1">
+        <v>61</v>
+      </c>
+      <c r="L72" s="11">
+        <f t="shared" si="0"/>
+        <v>0.32222222222222224</v>
+      </c>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
+      <c r="P72" s="1"/>
+      <c r="Q72" s="11"/>
+      <c r="S72" s="1">
+        <v>70172</v>
+      </c>
+      <c r="T72" s="1">
+        <v>90</v>
+      </c>
+      <c r="U72" s="1">
+        <v>58</v>
+      </c>
+      <c r="V72" s="11">
+        <f t="shared" si="1"/>
+        <v>0.35555555555555557</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="11"/>
+      <c r="I73" s="1">
+        <v>70181</v>
+      </c>
+      <c r="J73" s="1">
+        <v>109</v>
+      </c>
+      <c r="K73" s="1">
+        <v>29</v>
+      </c>
+      <c r="L73" s="12">
+        <f t="shared" si="0"/>
+        <v>0.73394495412844041</v>
+      </c>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="11"/>
+      <c r="S73" s="1">
+        <v>70181</v>
+      </c>
+      <c r="T73" s="1">
+        <v>128</v>
+      </c>
+      <c r="U73" s="1">
+        <v>91</v>
+      </c>
+      <c r="V73" s="11">
+        <f t="shared" si="1"/>
+        <v>0.2890625</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="11"/>
+      <c r="I74" s="1">
+        <v>70182</v>
+      </c>
+      <c r="J74" s="1">
+        <v>109</v>
+      </c>
+      <c r="K74" s="1">
+        <v>76</v>
+      </c>
+      <c r="L74" s="11">
+        <f t="shared" si="0"/>
+        <v>0.30275229357798167</v>
+      </c>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
+      <c r="P74" s="1"/>
+      <c r="Q74" s="11"/>
+      <c r="S74" s="1">
+        <v>70182</v>
+      </c>
+      <c r="T74" s="1">
+        <v>128</v>
+      </c>
+      <c r="U74" s="1">
+        <v>87</v>
+      </c>
+      <c r="V74" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3203125</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="11"/>
+      <c r="I75" s="1">
+        <v>70191</v>
+      </c>
+      <c r="J75" s="1">
+        <v>60</v>
+      </c>
+      <c r="K75" s="1">
+        <v>33</v>
+      </c>
+      <c r="L75" s="11">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="11"/>
+      <c r="S75" s="1">
+        <v>70191</v>
+      </c>
+      <c r="T75" s="1">
+        <v>90</v>
+      </c>
+      <c r="U75" s="1">
+        <v>73</v>
+      </c>
+      <c r="V75" s="11">
+        <f t="shared" si="1"/>
+        <v>0.18888888888888888</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="11"/>
+      <c r="I76" s="1">
+        <v>70192</v>
+      </c>
+      <c r="J76" s="1">
+        <v>60</v>
+      </c>
+      <c r="K76" s="1">
+        <v>26</v>
+      </c>
+      <c r="L76" s="11">
+        <f t="shared" si="0"/>
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="11"/>
+      <c r="S76" s="1">
+        <v>70192</v>
+      </c>
+      <c r="T76" s="1">
+        <v>90</v>
+      </c>
+      <c r="U76" s="1">
+        <v>73</v>
+      </c>
+      <c r="V76" s="11">
+        <f t="shared" si="1"/>
+        <v>0.18888888888888888</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="11"/>
+      <c r="I77" s="1">
+        <v>70201</v>
+      </c>
+      <c r="J77" s="1">
+        <v>81</v>
+      </c>
+      <c r="K77" s="1">
+        <v>38</v>
+      </c>
+      <c r="L77" s="11">
+        <f t="shared" si="0"/>
+        <v>0.53086419753086422</v>
+      </c>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="11"/>
+      <c r="S77" s="1">
+        <v>70201</v>
+      </c>
+      <c r="T77" s="1">
+        <v>90</v>
+      </c>
+      <c r="U77" s="1">
+        <v>62</v>
+      </c>
+      <c r="V77" s="11">
+        <f t="shared" si="1"/>
+        <v>0.31111111111111112</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="11"/>
+      <c r="I78" s="1">
+        <v>70202</v>
+      </c>
+      <c r="J78" s="1">
+        <v>81</v>
+      </c>
+      <c r="K78" s="1">
+        <v>45</v>
+      </c>
+      <c r="L78" s="11">
+        <f t="shared" si="0"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="11"/>
+      <c r="S78" s="1">
+        <v>70202</v>
+      </c>
+      <c r="T78" s="1">
+        <v>90</v>
+      </c>
+      <c r="U78" s="1">
+        <v>61</v>
+      </c>
+      <c r="V78" s="11">
+        <f t="shared" si="1"/>
+        <v>0.32222222222222224</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="11"/>
+      <c r="I79" s="1">
+        <v>70211</v>
+      </c>
+      <c r="J79" s="1">
+        <v>80</v>
+      </c>
+      <c r="K79" s="1">
+        <v>31</v>
+      </c>
+      <c r="L79" s="11">
+        <f t="shared" si="0"/>
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
+      <c r="P79" s="1"/>
+      <c r="Q79" s="11"/>
+      <c r="S79" s="1">
+        <v>70211</v>
+      </c>
+      <c r="T79" s="1">
+        <v>81</v>
+      </c>
+      <c r="U79" s="1">
+        <v>35</v>
+      </c>
+      <c r="V79" s="11">
+        <f t="shared" si="1"/>
+        <v>0.5679012345679012</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="11"/>
+      <c r="I80" s="1">
+        <v>70212</v>
+      </c>
+      <c r="J80" s="1">
+        <v>80</v>
+      </c>
+      <c r="K80" s="1">
+        <v>38</v>
+      </c>
+      <c r="L80" s="11">
+        <f t="shared" si="0"/>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1"/>
+      <c r="P80" s="1"/>
+      <c r="Q80" s="11"/>
+      <c r="S80" s="1">
+        <v>70212</v>
+      </c>
+      <c r="T80" s="1">
+        <v>81</v>
+      </c>
+      <c r="U80" s="1">
+        <v>28</v>
+      </c>
+      <c r="V80" s="11">
+        <f t="shared" si="1"/>
+        <v>0.65432098765432101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="11"/>
+      <c r="I81" s="1">
+        <v>70221</v>
+      </c>
+      <c r="J81" s="1">
+        <v>86</v>
+      </c>
+      <c r="K81" s="1">
+        <v>39</v>
+      </c>
+      <c r="L81" s="11">
+        <f t="shared" si="0"/>
+        <v>0.54651162790697672</v>
+      </c>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+      <c r="P81" s="1"/>
+      <c r="Q81" s="11"/>
+      <c r="S81" s="1">
+        <v>70221</v>
+      </c>
+      <c r="T81" s="1">
+        <v>79</v>
+      </c>
+      <c r="U81" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>19</v>
-      </c>
-      <c r="B58" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>20</v>
-      </c>
-      <c r="B59" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>21</v>
-      </c>
-      <c r="B60" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>22</v>
-      </c>
-      <c r="B61" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>23</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="V81" s="12">
+        <f t="shared" si="1"/>
+        <v>0.74683544303797467</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="11"/>
+      <c r="I82" s="1">
+        <v>70222</v>
+      </c>
+      <c r="J82" s="1">
+        <v>86</v>
+      </c>
+      <c r="K82" s="1">
+        <v>54</v>
+      </c>
+      <c r="L82" s="11">
+        <f t="shared" si="0"/>
+        <v>0.37209302325581395</v>
+      </c>
+      <c r="N82" s="1"/>
+      <c r="O82" s="1"/>
+      <c r="P82" s="1"/>
+      <c r="Q82" s="11"/>
+      <c r="S82" s="1">
+        <v>70222</v>
+      </c>
+      <c r="T82" s="1">
+        <v>79</v>
+      </c>
+      <c r="U82" s="1">
+        <v>42</v>
+      </c>
+      <c r="V82" s="11">
+        <f t="shared" si="1"/>
+        <v>0.46835443037974683</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="11"/>
+      <c r="I83" s="1">
+        <v>70231</v>
+      </c>
+      <c r="J83" s="1">
+        <v>70</v>
+      </c>
+      <c r="K83" s="1">
+        <v>35</v>
+      </c>
+      <c r="L83" s="11">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="11"/>
+      <c r="S83" s="1">
+        <v>70231</v>
+      </c>
+      <c r="T83" s="1">
+        <v>86</v>
+      </c>
+      <c r="U83" s="1">
+        <v>39</v>
+      </c>
+      <c r="V83" s="11">
+        <f t="shared" si="1"/>
+        <v>0.54651162790697672</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="11"/>
+      <c r="I84" s="1">
+        <v>70232</v>
+      </c>
+      <c r="J84" s="1">
+        <v>70</v>
+      </c>
+      <c r="K84" s="1">
+        <v>42</v>
+      </c>
+      <c r="L84" s="11">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="N84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="1"/>
+      <c r="Q84" s="11"/>
+      <c r="S84" s="1">
+        <v>70232</v>
+      </c>
+      <c r="T84" s="1">
+        <v>86</v>
+      </c>
+      <c r="U84" s="1">
+        <v>54</v>
+      </c>
+      <c r="V84" s="11">
+        <f t="shared" si="1"/>
+        <v>0.37209302325581395</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="11"/>
+      <c r="I85" s="1">
+        <v>70241</v>
+      </c>
+      <c r="J85" s="1">
+        <v>29</v>
+      </c>
+      <c r="K85" s="1">
+        <v>29</v>
+      </c>
+      <c r="L85" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="11"/>
+      <c r="S85" s="1">
+        <v>70241</v>
+      </c>
+      <c r="T85" s="1">
+        <v>70</v>
+      </c>
+      <c r="U85" s="1">
+        <v>35</v>
+      </c>
+      <c r="V85" s="11">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="11"/>
+      <c r="I86" s="1">
+        <v>70242</v>
+      </c>
+      <c r="J86" s="1">
+        <v>29</v>
+      </c>
+      <c r="K86" s="1">
+        <v>27</v>
+      </c>
+      <c r="L86" s="11">
+        <f t="shared" si="0"/>
+        <v>6.8965517241379309E-2</v>
+      </c>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="11"/>
+      <c r="S86" s="1">
+        <v>70242</v>
+      </c>
+      <c r="T86" s="1">
+        <v>70</v>
+      </c>
+      <c r="U86" s="1">
+        <v>42</v>
+      </c>
+      <c r="V86" s="11">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="11"/>
+      <c r="I87" s="1">
+        <v>70251</v>
+      </c>
+      <c r="J87" s="1">
+        <v>28</v>
+      </c>
+      <c r="K87" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>24</v>
-      </c>
-      <c r="B63" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>25</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="L87" s="11">
+        <f t="shared" si="0"/>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="N87" s="1"/>
+      <c r="O87" s="1"/>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="11"/>
+      <c r="S87" s="1">
+        <v>70251</v>
+      </c>
+      <c r="T87" s="1">
+        <v>29</v>
+      </c>
+      <c r="U87" s="1">
+        <v>29</v>
+      </c>
+      <c r="V87" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="11"/>
+      <c r="I88" s="1">
+        <v>70252</v>
+      </c>
+      <c r="J88" s="1">
+        <v>28</v>
+      </c>
+      <c r="K88" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>26</v>
-      </c>
-      <c r="B65" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="L88" s="11">
+        <f t="shared" si="0"/>
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="11"/>
+      <c r="S88" s="1">
+        <v>70252</v>
+      </c>
+      <c r="T88" s="1">
+        <v>29</v>
+      </c>
+      <c r="U88" s="1">
         <v>27</v>
       </c>
-      <c r="B66" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>28</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="V88" s="11">
+        <f t="shared" si="1"/>
+        <v>6.8965517241379309E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="11"/>
+      <c r="I89" s="1">
+        <v>70261</v>
+      </c>
+      <c r="J89" s="1">
+        <v>98</v>
+      </c>
+      <c r="K89" s="1">
+        <v>54</v>
+      </c>
+      <c r="L89" s="11">
+        <f t="shared" si="0"/>
+        <v>0.44897959183673469</v>
+      </c>
+      <c r="N89" s="1"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="11"/>
+      <c r="S89" s="1">
+        <v>70261</v>
+      </c>
+      <c r="T89" s="1">
+        <v>66</v>
+      </c>
+      <c r="U89" s="1">
+        <v>48</v>
+      </c>
+      <c r="V89" s="11">
+        <f t="shared" si="1"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="11"/>
+      <c r="I90" s="1">
+        <v>70262</v>
+      </c>
+      <c r="J90" s="1">
+        <v>98</v>
+      </c>
+      <c r="K90" s="1">
+        <v>40</v>
+      </c>
+      <c r="L90" s="11">
+        <f t="shared" si="0"/>
+        <v>0.59183673469387754</v>
+      </c>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="11"/>
+      <c r="S90" s="1">
+        <v>70262</v>
+      </c>
+      <c r="T90" s="1">
+        <v>66</v>
+      </c>
+      <c r="U90" s="1">
+        <v>52</v>
+      </c>
+      <c r="V90" s="11">
+        <f t="shared" si="1"/>
+        <v>0.21212121212121213</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="11"/>
+      <c r="I91" s="1">
+        <v>70271</v>
+      </c>
+      <c r="J91" s="1">
+        <v>66</v>
+      </c>
+      <c r="K91" s="1">
+        <v>48</v>
+      </c>
+      <c r="L91" s="11">
+        <f t="shared" si="0"/>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="N91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="11"/>
+      <c r="S91" s="1">
+        <v>70271</v>
+      </c>
+      <c r="T91" s="1">
+        <v>120</v>
+      </c>
+      <c r="U91" s="1">
+        <v>81</v>
+      </c>
+      <c r="V91" s="11">
+        <f t="shared" si="1"/>
+        <v>0.32500000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="11"/>
+      <c r="I92" s="1">
+        <v>70272</v>
+      </c>
+      <c r="J92" s="1">
+        <v>66</v>
+      </c>
+      <c r="K92" s="1">
+        <v>52</v>
+      </c>
+      <c r="L92" s="11">
+        <f t="shared" si="0"/>
+        <v>0.21212121212121213</v>
+      </c>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="11"/>
+      <c r="S92" s="1">
+        <v>70272</v>
+      </c>
+      <c r="T92" s="1">
+        <v>120</v>
+      </c>
+      <c r="U92" s="1">
+        <v>93</v>
+      </c>
+      <c r="V92" s="11">
+        <f t="shared" si="1"/>
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="11"/>
+      <c r="I93" s="1">
+        <v>70281</v>
+      </c>
+      <c r="J93" s="1">
+        <v>120</v>
+      </c>
+      <c r="K93" s="1">
+        <v>81</v>
+      </c>
+      <c r="L93" s="11">
+        <f t="shared" si="0"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="11"/>
+      <c r="S93" s="1">
+        <v>70281</v>
+      </c>
+      <c r="T93" s="1">
+        <v>60</v>
+      </c>
+      <c r="U93" s="1">
+        <v>35</v>
+      </c>
+      <c r="V93" s="11">
+        <f t="shared" si="1"/>
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="11"/>
+      <c r="I94" s="1">
+        <v>70282</v>
+      </c>
+      <c r="J94" s="1">
+        <v>120</v>
+      </c>
+      <c r="K94" s="1">
+        <v>93</v>
+      </c>
+      <c r="L94" s="11">
+        <f t="shared" si="0"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="11"/>
+      <c r="S94" s="1">
+        <v>70282</v>
+      </c>
+      <c r="T94" s="1">
+        <v>60</v>
+      </c>
+      <c r="U94" s="1">
+        <v>38</v>
+      </c>
+      <c r="V94" s="11">
+        <f t="shared" si="1"/>
+        <v>0.36666666666666664</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="11"/>
+      <c r="I95" s="1">
+        <v>70291</v>
+      </c>
+      <c r="J95" s="1">
+        <v>60</v>
+      </c>
+      <c r="K95" s="1">
+        <v>40</v>
+      </c>
+      <c r="L95" s="11">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1"/>
+      <c r="Q95" s="11"/>
+      <c r="S95" s="1">
+        <v>70291</v>
+      </c>
+      <c r="T95" s="1">
+        <v>39</v>
+      </c>
+      <c r="U95" s="1">
+        <v>36</v>
+      </c>
+      <c r="V95" s="11">
+        <f t="shared" si="1"/>
+        <v>7.6923076923076927E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="11"/>
+      <c r="I96" s="1">
+        <v>70292</v>
+      </c>
+      <c r="J96" s="1">
+        <v>60</v>
+      </c>
+      <c r="K96" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>29</v>
-      </c>
-      <c r="B68" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>30</v>
-      </c>
-      <c r="B69" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>31</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>32</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>33</v>
-      </c>
-      <c r="B72" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>34</v>
-      </c>
-      <c r="B73" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>35</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="L96" s="11">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="N96" s="1"/>
+      <c r="O96" s="1"/>
+      <c r="P96" s="1"/>
+      <c r="Q96" s="11"/>
+      <c r="S96" s="1">
+        <v>70292</v>
+      </c>
+      <c r="T96" s="1">
+        <v>39</v>
+      </c>
+      <c r="U96" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>36</v>
-      </c>
-      <c r="B75" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>37</v>
-      </c>
-      <c r="B76" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>38</v>
-      </c>
-      <c r="B77" t="s">
+      <c r="V96" s="11">
+        <f t="shared" si="1"/>
+        <v>5.128205128205128E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="11"/>
+      <c r="I97" s="1">
+        <v>70301</v>
+      </c>
+      <c r="J97" s="1">
+        <v>58</v>
+      </c>
+      <c r="K97" s="1">
+        <v>51</v>
+      </c>
+      <c r="L97" s="11">
+        <f t="shared" si="0"/>
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="N97" s="1"/>
+      <c r="O97" s="1"/>
+      <c r="P97" s="1"/>
+      <c r="Q97" s="11"/>
+      <c r="S97" s="1">
+        <v>70301</v>
+      </c>
+      <c r="T97" s="1">
+        <v>58</v>
+      </c>
+      <c r="U97" s="1">
+        <v>51</v>
+      </c>
+      <c r="V97" s="11">
+        <f t="shared" si="1"/>
+        <v>0.1206896551724138</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="11"/>
+      <c r="I98" s="1">
+        <v>70302</v>
+      </c>
+      <c r="J98" s="1">
+        <v>58</v>
+      </c>
+      <c r="K98" s="1">
+        <v>42</v>
+      </c>
+      <c r="L98" s="11">
+        <f t="shared" si="0"/>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="N98" s="1"/>
+      <c r="O98" s="1"/>
+      <c r="P98" s="1"/>
+      <c r="Q98" s="11"/>
+      <c r="S98" s="1">
+        <v>70302</v>
+      </c>
+      <c r="T98" s="1">
+        <v>58</v>
+      </c>
+      <c r="U98" s="1">
+        <v>42</v>
+      </c>
+      <c r="V98" s="11">
+        <f t="shared" si="1"/>
+        <v>0.27586206896551724</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
+      <c r="K100" s="14" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>39</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="L100" s="15">
+        <f>AVERAGE(L39:L98)</f>
+        <v>0.33902835377727603</v>
+      </c>
+      <c r="M100" s="13"/>
+      <c r="N100" s="13"/>
+      <c r="O100" s="13"/>
+      <c r="P100" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q100" s="15" t="e">
+        <f>AVERAGE(Q39:Q98)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R100" s="13"/>
+      <c r="S100" s="13"/>
+      <c r="T100" s="13"/>
+      <c r="U100" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="V100" s="15">
+        <f>AVERAGE(V39:V98)</f>
+        <v>0.29576946830311535</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I101" s="13"/>
+      <c r="J101" s="13"/>
+      <c r="K101" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>40</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="L101" s="15">
+        <f>MAX(L39:L98)</f>
+        <v>0.73394495412844041</v>
+      </c>
+      <c r="M101" s="13"/>
+      <c r="N101" s="13"/>
+      <c r="O101" s="13"/>
+      <c r="P101" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q101" s="15">
+        <f>MAX(Q39:Q98)</f>
+        <v>0</v>
+      </c>
+      <c r="R101" s="13"/>
+      <c r="S101" s="13"/>
+      <c r="T101" s="13"/>
+      <c r="U101" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="V101" s="15">
+        <f>MAX(V39:V98)</f>
+        <v>0.74683544303797467</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I102" s="13"/>
+      <c r="J102" s="13"/>
+      <c r="K102" s="13"/>
+      <c r="L102" s="13"/>
+      <c r="M102" s="13"/>
+      <c r="N102" s="13"/>
+      <c r="O102" s="13"/>
+      <c r="P102" s="13"/>
+      <c r="Q102" s="13"/>
+      <c r="R102" s="13"/>
+      <c r="S102" s="13"/>
+      <c r="T102" s="13"/>
+      <c r="U102" s="13"/>
+      <c r="V102" s="13"/>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I103" s="14" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>41</v>
-      </c>
-      <c r="B80" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+      <c r="J103" s="16">
+        <f>SUM(J39:J98)</f>
+        <v>4800</v>
+      </c>
+      <c r="K103" s="16">
+        <f>SUM(K39:K98)</f>
+        <v>3004</v>
+      </c>
+      <c r="L103" s="13"/>
+      <c r="M103" s="13"/>
+      <c r="N103" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B81" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>43</v>
-      </c>
-      <c r="B82" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>44</v>
-      </c>
-      <c r="B83" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>45</v>
-      </c>
-      <c r="B84" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>46</v>
-      </c>
-      <c r="B85" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>47</v>
-      </c>
-      <c r="B86" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>48</v>
-      </c>
-      <c r="B87" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>49</v>
-      </c>
-      <c r="B88" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>50</v>
-      </c>
-      <c r="B89" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>51</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>52</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>53</v>
-      </c>
-      <c r="B92" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>54</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>55</v>
-      </c>
-      <c r="B94" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>56</v>
-      </c>
-      <c r="B95" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>57</v>
-      </c>
-      <c r="B96" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>58</v>
-      </c>
-      <c r="B97" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>59</v>
-      </c>
-      <c r="B98" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>60</v>
-      </c>
-      <c r="B99" t="s">
-        <v>62</v>
-      </c>
+      <c r="O103" s="16">
+        <f>SUM(O39:O98)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="16">
+        <f>SUM(P39:P98)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="13"/>
+      <c r="R103" s="13"/>
+      <c r="S103" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="T103" s="16">
+        <f>SUM(T39:T98)</f>
+        <v>4806</v>
+      </c>
+      <c r="U103" s="16">
+        <f>SUM(U39:U98)</f>
+        <v>3270</v>
+      </c>
+      <c r="V103" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="S2:U2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="N2:P2"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="E2:G2"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2851,29 +6633,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>79</v>
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2881,12 +6663,12 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1">
         <v>1952</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="7">
         <v>0.13274900000000001</v>
       </c>
       <c r="E2" s="1"/>
@@ -2905,12 +6687,12 @@
         <v>78</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1">
         <v>1971</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="7">
         <v>0.154025</v>
       </c>
       <c r="E3" s="1"/>
@@ -2929,12 +6711,12 @@
         <v>963</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1">
         <v>1994</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="7">
         <v>0.57111400000000001</v>
       </c>
       <c r="E4" s="1"/>
@@ -2953,12 +6735,12 @@
         <v>1166</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <v>1999</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="7">
         <v>0.124177</v>
       </c>
       <c r="E5" s="1"/>
@@ -2977,12 +6759,12 @@
         <v>1286</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>1999</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="7">
         <v>0.12634200000000001</v>
       </c>
       <c r="E6" s="1"/>
@@ -3001,12 +6783,12 @@
         <v>1292</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1">
         <v>1999</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="7">
         <v>0.189635</v>
       </c>
       <c r="E7" s="1"/>
@@ -3025,12 +6807,12 @@
         <v>1297</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
         <v>1999</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="7">
         <v>0.168541</v>
       </c>
       <c r="E8" s="1"/>
@@ -3049,12 +6831,12 @@
         <v>1436</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1">
         <v>1999</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="7">
         <v>0.13097</v>
       </c>
       <c r="E9" s="1"/>
@@ -3073,12 +6855,12 @@
         <v>1465</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1">
         <v>1999</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="7">
         <v>7.3763999999999996E-2</v>
       </c>
       <c r="E10" s="1"/>
@@ -3097,12 +6879,12 @@
         <v>1469</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <v>1999</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="7">
         <v>7.2117000000000001E-2</v>
       </c>
       <c r="E11" s="1"/>
@@ -3121,12 +6903,12 @@
         <v>1470</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1">
         <v>1999</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="7">
         <v>7.5738E-2</v>
       </c>
       <c r="E12" s="1"/>
@@ -3145,12 +6927,12 @@
         <v>1472</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1">
         <v>1999</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="7">
         <v>0.125749</v>
       </c>
       <c r="E13" s="1"/>
@@ -3169,12 +6951,12 @@
         <v>1478</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1">
         <v>1999</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="7">
         <v>0.18559500000000001</v>
       </c>
       <c r="E14" s="1"/>
@@ -3193,12 +6975,12 @@
         <v>1485</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1">
         <v>1999</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="7">
         <v>0.51015200000000005</v>
       </c>
       <c r="E15" s="1"/>
@@ -3217,12 +6999,12 @@
         <v>1487</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1">
         <v>1999</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="7">
         <v>0.40849800000000003</v>
       </c>
       <c r="E16" s="1"/>
@@ -3241,12 +7023,12 @@
         <v>1524</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
         <v>1999</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="7">
         <v>0.70477000000000001</v>
       </c>
       <c r="E17" s="1"/>
@@ -3265,12 +7047,12 @@
         <v>1555</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1">
         <v>1999</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="7">
         <v>0.1341</v>
       </c>
       <c r="E18" s="1"/>
@@ -3289,12 +7071,12 @@
         <v>1557</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
         <v>1999</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="7">
         <v>9.6298999999999996E-2</v>
       </c>
       <c r="E19" s="1"/>
@@ -3313,12 +7095,12 @@
         <v>1575</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1">
         <v>1999</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="7">
         <v>6.6946000000000006E-2</v>
       </c>
       <c r="E20" s="1"/>
@@ -3337,12 +7119,12 @@
         <v>1581</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1">
         <v>1999</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="7">
         <v>8.5407999999999998E-2</v>
       </c>
       <c r="E21" s="1"/>
@@ -3361,12 +7143,12 @@
         <v>2466</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1">
         <v>1999</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="7">
         <v>0.20050699999999999</v>
       </c>
       <c r="E22" s="1"/>
@@ -3385,12 +7167,12 @@
         <v>3274</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C23" s="1">
         <v>1999</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="7">
         <v>0.170517</v>
       </c>
       <c r="E23" s="1"/>
@@ -3409,12 +7191,12 @@
         <v>3281</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C24" s="1">
         <v>1999</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="7">
         <v>0.13556599999999999</v>
       </c>
       <c r="E24" s="1"/>
@@ -3433,12 +7215,12 @@
         <v>3307</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1">
         <v>1999</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="7">
         <v>0.26130199999999998</v>
       </c>
       <c r="E25" s="1"/>
@@ -3457,12 +7239,12 @@
         <v>3750</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1">
         <v>1992</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="7">
         <v>0.19967699999999999</v>
       </c>
       <c r="E26" s="1"/>
@@ -3481,12 +7263,12 @@
         <v>3751</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="C27" s="1">
         <v>1992</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="7">
         <v>9.5811999999999994E-2</v>
       </c>
       <c r="E27" s="1"/>
@@ -3505,16 +7287,16 @@
         <v>4350</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1">
         <v>1997</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="7">
         <v>0.121834</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="14">
+      <c r="F28" s="8">
         <v>6</v>
       </c>
       <c r="G28" s="1">
@@ -3529,12 +7311,12 @@
         <v>4884</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="C29" s="1">
         <v>2007</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="7">
         <v>0.767988</v>
       </c>
       <c r="E29" s="1"/>
@@ -3553,12 +7335,12 @@
         <v>5663</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="C30" s="1">
         <v>2008</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="7">
         <v>0.705318</v>
       </c>
       <c r="E30" s="1"/>
@@ -3577,12 +7359,12 @@
         <v>5778</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="C31" s="1">
         <v>2008</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="7">
         <v>0.296213</v>
       </c>
       <c r="E31" s="1"/>

--- a/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
+++ b/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\StaticDynamicAnalysis\ida-spo-msa\HazardAnalysis\gm-selection\2020_NBC_MyCopy_new-main\GMSelection_NGA_KiK_mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541834EC-E414-480F-AD96-62E83F5A9936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11366C7-5392-4258-9E8C-349CBB882B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GMSel_ΔM (±)" sheetId="1" r:id="rId1"/>
     <sheet name="EQ-Infor_Guw-BCH" sheetId="2" r:id="rId2"/>
     <sheet name="CY14-effectOnMIDR_RDR_PFA" sheetId="4" r:id="rId3"/>
     <sheet name="BCH16-effectOnMIDR_RDR_PFA" sheetId="3" r:id="rId4"/>
+    <sheet name="effectOnMIDR_RDR_PFA" sheetId="6" r:id="rId5"/>
+    <sheet name="OutputMemorySize" sheetId="5" r:id="rId6"/>
+    <sheet name="epsilon_bar" sheetId="7" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="173">
   <si>
     <t>SNo</t>
   </si>
@@ -434,6 +434,168 @@
   <si>
     <t>3) PFA has increased after curtailment, curtailed response more than the original GM response</t>
   </si>
+  <si>
+    <t>EQ_70011</t>
+  </si>
+  <si>
+    <t>EQ_70012</t>
+  </si>
+  <si>
+    <t>EQ_70021</t>
+  </si>
+  <si>
+    <t>EQ_70022</t>
+  </si>
+  <si>
+    <t>EleGlobalTH</t>
+  </si>
+  <si>
+    <t>EleLocalTH</t>
+  </si>
+  <si>
+    <t>Hinges</t>
+  </si>
+  <si>
+    <t>Joints</t>
+  </si>
+  <si>
+    <t>These are the springs at the base of the columns</t>
+  </si>
+  <si>
+    <t>joint numbers to record - all joints of primary frame</t>
+  </si>
+  <si>
+    <t>computing base shear and story shear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set elementNumToRecordLIST { </t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set hingeElementsToRecordLIST  { </t>
+  </si>
+  <si>
+    <t xml:space="preserve">set jointNumToRecordLIST { </t>
+  </si>
+  <si>
+    <t>originalSize (GB)</t>
+  </si>
+  <si>
+    <t>RecordTurnoff in Elements folder (MB)</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>MIDR (%)</t>
+  </si>
+  <si>
+    <t>RDR (%)</t>
+  </si>
+  <si>
+    <t>AllComp</t>
+  </si>
+  <si>
+    <t>1 (%)</t>
+  </si>
+  <si>
+    <t>4 (%)</t>
+  </si>
+  <si>
+    <t>0.2 (%)</t>
+  </si>
+  <si>
+    <t>0.5 (%)</t>
+  </si>
+  <si>
+    <t>GMPM</t>
+  </si>
+  <si>
+    <t>TimeP</t>
+  </si>
+  <si>
+    <t>pred_mean (g)</t>
+  </si>
+  <si>
+    <t>sigma_Ln</t>
+  </si>
+  <si>
+    <t>epsilon_bar</t>
+  </si>
+  <si>
+    <t>BJF97</t>
+  </si>
+  <si>
+    <t>AS97</t>
+  </si>
+  <si>
+    <t>BA08</t>
+  </si>
+  <si>
+    <t>C97</t>
+  </si>
+  <si>
+    <t>ASB96</t>
+  </si>
+  <si>
+    <t>BSSA14</t>
+  </si>
+  <si>
+    <t>CB14</t>
+  </si>
+  <si>
+    <t>AB03SZ</t>
+  </si>
+  <si>
+    <t>Zhao06</t>
+  </si>
+  <si>
+    <t>eps_bar</t>
+  </si>
+  <si>
+    <t>PSHA_mean IM (g)</t>
+  </si>
+  <si>
+    <t>CollapseMechanism, 2 (%)</t>
+  </si>
+  <si>
+    <t>ControlComp</t>
+  </si>
+  <si>
+    <t>2 (%)</t>
+  </si>
+  <si>
+    <t>CollapseMechanism, 12 (%)</t>
+  </si>
+  <si>
+    <t>PFA (%)</t>
+  </si>
+  <si>
+    <t>0.2g</t>
+  </si>
+  <si>
+    <t>0.5g</t>
+  </si>
+  <si>
+    <t>1g</t>
+  </si>
+  <si>
+    <t>CollapseMechanism, 2g</t>
+  </si>
+  <si>
+    <t>PFA</t>
+  </si>
+  <si>
+    <t>1) Curtailed GMs lower median collapse IM (more damaging)</t>
+  </si>
+  <si>
+    <t>1) No change in median capacity</t>
+  </si>
+  <si>
+    <t>1) Not much significant variation in median capacity between original and curtailed GMs</t>
+  </si>
 </sst>
 </file>
 
@@ -443,7 +605,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,8 +731,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -615,8 +791,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -737,6 +919,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -745,7 +936,7 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -822,6 +1013,49 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="4" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -846,6 +1080,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Calculation" xfId="4" builtinId="22"/>
@@ -13354,1041 +13589,2056 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="original&amp;curtailedComparision"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="B4">
-            <v>70011</v>
-          </cell>
-          <cell r="F4">
-            <v>3.9324935897435999E-2</v>
-          </cell>
-          <cell r="G4">
-            <v>3.9324935897435999E-2</v>
-          </cell>
-          <cell r="I4">
-            <v>2.1838698362420002</v>
-          </cell>
-          <cell r="J4">
-            <v>2.1838698362420002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5">
-            <v>70012</v>
-          </cell>
-          <cell r="F5">
-            <v>6.4746777777778E-2</v>
-          </cell>
-          <cell r="G5">
-            <v>6.4746777777778E-2</v>
-          </cell>
-          <cell r="I5">
-            <v>2.2740035374557701</v>
-          </cell>
-          <cell r="J5">
-            <v>2.2740035374557701</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>70021</v>
-          </cell>
-          <cell r="F6">
-            <v>6.6656025641026004E-2</v>
-          </cell>
-          <cell r="G6">
-            <v>6.5797692307692002E-2</v>
-          </cell>
-          <cell r="I6">
-            <v>1.72492936144258</v>
-          </cell>
-          <cell r="J6">
-            <v>2.4762036412481101</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7">
-            <v>70022</v>
-          </cell>
-          <cell r="F7">
-            <v>1.2490230769231E-2</v>
-          </cell>
-          <cell r="G7">
-            <v>1.3455384615385001E-2</v>
-          </cell>
-          <cell r="I7">
-            <v>1.64008751421943</v>
-          </cell>
-          <cell r="J7">
-            <v>2.4214257397106702</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>70031</v>
-          </cell>
-          <cell r="F8">
-            <v>9.3543444444443999E-2</v>
-          </cell>
-          <cell r="G8">
-            <v>9.2749666666666994E-2</v>
-          </cell>
-          <cell r="I8">
-            <v>3.3060718823790101</v>
-          </cell>
-          <cell r="J8">
-            <v>3.3785302919788598</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9">
-            <v>70032</v>
-          </cell>
-          <cell r="F9">
-            <v>9.6754615384614995E-2</v>
-          </cell>
-          <cell r="G9">
-            <v>9.6198974358973996E-2</v>
-          </cell>
-          <cell r="I9">
-            <v>2.4197413669649901</v>
-          </cell>
-          <cell r="J9">
-            <v>2.5646611110796602</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10">
-            <v>70041</v>
-          </cell>
-          <cell r="F10">
-            <v>6.2362333333332999E-2</v>
-          </cell>
-          <cell r="G10">
-            <v>5.2130897435897001E-2</v>
-          </cell>
-          <cell r="I10">
-            <v>1.08602832889904</v>
-          </cell>
-          <cell r="J10">
-            <v>1.0133089502261201</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11">
-            <v>70042</v>
-          </cell>
-          <cell r="F11">
-            <v>4.9905888888889E-2</v>
-          </cell>
-          <cell r="G11">
-            <v>4.9377555555556001E-2</v>
-          </cell>
-          <cell r="I11">
-            <v>1.8680950896058801</v>
-          </cell>
-          <cell r="J11">
-            <v>2.03814017527047</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12">
-            <v>70051</v>
-          </cell>
-          <cell r="F12">
-            <v>2.116108974359E-2</v>
-          </cell>
-          <cell r="G12">
-            <v>2.0970333333333001E-2</v>
-          </cell>
-          <cell r="I12">
-            <v>1.9346491127859899</v>
-          </cell>
-          <cell r="J12">
-            <v>1.9346491127859899</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13">
-            <v>70052</v>
-          </cell>
-          <cell r="F13">
-            <v>7.6251153846153996E-2</v>
-          </cell>
-          <cell r="G13">
-            <v>7.6245384615385006E-2</v>
-          </cell>
-          <cell r="I13">
-            <v>2.8936185170640201</v>
-          </cell>
-          <cell r="J13">
-            <v>2.8936185170640201</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14">
-            <v>70061</v>
-          </cell>
-          <cell r="F14">
-            <v>7.0354333333333005E-2</v>
-          </cell>
-          <cell r="G14">
-            <v>7.0643888888889006E-2</v>
-          </cell>
-          <cell r="I14">
-            <v>1.62114389608052</v>
-          </cell>
-          <cell r="J14">
-            <v>1.96271854483804</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15">
-            <v>70062</v>
-          </cell>
-          <cell r="F15" t="str">
-            <v>NA</v>
-          </cell>
-          <cell r="G15" t="str">
-            <v>NA</v>
-          </cell>
-          <cell r="I15">
-            <v>1.89741392653293</v>
-          </cell>
-          <cell r="J15">
-            <v>1.7734045389062201</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16">
-            <v>70071</v>
-          </cell>
-          <cell r="F16">
-            <v>4.0636222222221997E-2</v>
-          </cell>
-          <cell r="G16" t="str">
-            <v>NA</v>
-          </cell>
-          <cell r="I16">
-            <v>1.4195102931855099</v>
-          </cell>
-          <cell r="J16">
-            <v>1.42269119184335</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17">
-            <v>70072</v>
-          </cell>
-          <cell r="F17">
-            <v>2.8804111111110999E-2</v>
-          </cell>
-          <cell r="G17">
-            <v>2.8670333333332999E-2</v>
-          </cell>
-          <cell r="I17">
-            <v>1.11627875064999</v>
-          </cell>
-          <cell r="J17">
-            <v>1.32870239048572</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18">
-            <v>70081</v>
-          </cell>
-          <cell r="F18">
-            <v>2.9021564102563999E-2</v>
-          </cell>
-          <cell r="G18">
-            <v>2.9021564102563999E-2</v>
-          </cell>
-          <cell r="I18">
-            <v>1.31187848561793</v>
-          </cell>
-          <cell r="J18">
-            <v>1.31187848561793</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19">
-            <v>70082</v>
-          </cell>
-          <cell r="F19">
-            <v>1.3512944444444E-2</v>
-          </cell>
-          <cell r="G19">
-            <v>1.3512944444444E-2</v>
-          </cell>
-          <cell r="I19">
-            <v>1.3353587449472899</v>
-          </cell>
-          <cell r="J19">
-            <v>1.3353587449472899</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20">
-            <v>70091</v>
-          </cell>
-          <cell r="F20">
-            <v>7.1193333333330003E-3</v>
-          </cell>
-          <cell r="G20">
-            <v>6.6056923076920002E-3</v>
-          </cell>
-          <cell r="I20">
-            <v>1.84650010939104</v>
-          </cell>
-          <cell r="J20">
-            <v>2.5930285685308299</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21">
-            <v>70092</v>
-          </cell>
-          <cell r="F21">
-            <v>1.9380666666667001E-2</v>
-          </cell>
-          <cell r="G21">
-            <v>1.9127769230769E-2</v>
-          </cell>
-          <cell r="I21">
-            <v>1.5211064059030399</v>
-          </cell>
-          <cell r="J21">
-            <v>1.88498273453623</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22">
-            <v>70101</v>
-          </cell>
-          <cell r="F22">
-            <v>1.493242333333E-3</v>
-          </cell>
-          <cell r="G22">
-            <v>1.459031E-3</v>
-          </cell>
-          <cell r="I22">
-            <v>1.7770237469732799</v>
-          </cell>
-          <cell r="J22">
-            <v>1.9822925254803601</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23">
-            <v>70102</v>
-          </cell>
-          <cell r="F23">
-            <v>1.0675962222222E-2</v>
-          </cell>
-          <cell r="G23">
-            <v>1.0689663333333E-2</v>
-          </cell>
-          <cell r="I23">
-            <v>1.75071461836188</v>
-          </cell>
-          <cell r="J23">
-            <v>2.0955184211525002</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24">
-            <v>70111</v>
-          </cell>
-          <cell r="F24">
-            <v>6.1813333333332998E-2</v>
-          </cell>
-          <cell r="G24">
-            <v>6.6582179487178997E-2</v>
-          </cell>
-          <cell r="I24">
-            <v>4.5515170569623997</v>
-          </cell>
-          <cell r="J24">
-            <v>4.6183246685698798</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25">
-            <v>70112</v>
-          </cell>
-          <cell r="F25">
-            <v>8.9359111111111E-2</v>
-          </cell>
-          <cell r="G25">
-            <v>8.3421555555555998E-2</v>
-          </cell>
-          <cell r="I25">
-            <v>5.0281870530882804</v>
-          </cell>
-          <cell r="J25">
-            <v>4.17111568746631</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26">
-            <v>70121</v>
-          </cell>
-          <cell r="F26">
-            <v>5.1444777777777999E-2</v>
-          </cell>
-          <cell r="G26">
-            <v>4.1850666666667001E-2</v>
-          </cell>
-          <cell r="I26">
-            <v>1.41192659540084</v>
-          </cell>
-          <cell r="J26">
-            <v>1.4525204325198999</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27">
-            <v>70122</v>
-          </cell>
-          <cell r="F27">
-            <v>3.9110555555556002E-2</v>
-          </cell>
-          <cell r="G27">
-            <v>3.9121222222222002E-2</v>
-          </cell>
-          <cell r="I27">
-            <v>1.17375786499302</v>
-          </cell>
-          <cell r="J27">
-            <v>1.37214856256421</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28">
-            <v>70131</v>
-          </cell>
-          <cell r="F28">
-            <v>2.7108717948718001E-2</v>
-          </cell>
-          <cell r="G28">
-            <v>2.7050769230769E-2</v>
-          </cell>
-          <cell r="I28">
-            <v>2.7181844065263299</v>
-          </cell>
-          <cell r="J28">
-            <v>4.2197347770554501</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29">
-            <v>70132</v>
-          </cell>
-          <cell r="F29">
-            <v>5.7151794871795003E-2</v>
-          </cell>
-          <cell r="G29">
-            <v>4.3554615384614997E-2</v>
-          </cell>
-          <cell r="I29">
-            <v>4.1606974018364902</v>
-          </cell>
-          <cell r="J29">
-            <v>4.2697309953165599</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30">
-            <v>70141</v>
-          </cell>
-          <cell r="F30">
-            <v>1.5205822222222E-2</v>
-          </cell>
-          <cell r="G30">
-            <v>1.5208444444444E-2</v>
-          </cell>
-          <cell r="I30">
-            <v>1.1651743159657499</v>
-          </cell>
-          <cell r="J30">
-            <v>1.2242925908820299</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31">
-            <v>70142</v>
-          </cell>
-          <cell r="F31">
-            <v>6.4213111111110999E-2</v>
-          </cell>
-          <cell r="G31">
-            <v>6.2148111111111001E-2</v>
-          </cell>
-          <cell r="I31">
-            <v>1.4296897000997399</v>
-          </cell>
-          <cell r="J31">
-            <v>1.49891624237332</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32">
-            <v>70151</v>
-          </cell>
-          <cell r="F32">
-            <v>1.7603769230768999E-2</v>
-          </cell>
-          <cell r="G32">
-            <v>1.7778192307691999E-2</v>
-          </cell>
-          <cell r="I32">
-            <v>1.6788213190435699</v>
-          </cell>
-          <cell r="J32">
-            <v>1.8107028616290599</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33">
-            <v>70152</v>
-          </cell>
-          <cell r="F33">
-            <v>1.2571577777778E-2</v>
-          </cell>
-          <cell r="G33">
-            <v>1.25956E-2</v>
-          </cell>
-          <cell r="I33">
-            <v>1.65731329562257</v>
-          </cell>
-          <cell r="J33">
-            <v>1.5990810056517999</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34">
-            <v>70161</v>
-          </cell>
-          <cell r="F34">
-            <v>3.4828111111110997E-2</v>
-          </cell>
-          <cell r="G34">
-            <v>3.4697777777778001E-2</v>
-          </cell>
-          <cell r="I34">
-            <v>1.2933847527067901</v>
-          </cell>
-          <cell r="J34">
-            <v>1.39219157172692</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35">
-            <v>70162</v>
-          </cell>
-          <cell r="F35">
-            <v>7.6926888888889003E-2</v>
-          </cell>
-          <cell r="G35">
-            <v>7.6874333333333003E-2</v>
-          </cell>
-          <cell r="I35">
-            <v>1.24930895758254</v>
-          </cell>
-          <cell r="J35">
-            <v>1.39246836724477</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36">
-            <v>70171</v>
-          </cell>
-          <cell r="F36">
-            <v>4.2286461538462002E-2</v>
-          </cell>
-          <cell r="G36">
-            <v>4.2273999999999999E-2</v>
-          </cell>
-          <cell r="I36">
-            <v>1.2830753043360501</v>
-          </cell>
-          <cell r="J36">
-            <v>1.75730035444545</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37">
-            <v>70172</v>
-          </cell>
-          <cell r="F37">
-            <v>5.0994999999999999E-2</v>
-          </cell>
-          <cell r="G37">
-            <v>5.0962222222221999E-2</v>
-          </cell>
-          <cell r="I37">
-            <v>1.0987305321683201</v>
-          </cell>
-          <cell r="J37">
-            <v>1.4784673623084801</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38">
-            <v>70181</v>
-          </cell>
-          <cell r="F38">
-            <v>6.8851538461538006E-2</v>
-          </cell>
-          <cell r="G38">
-            <v>6.8240384615384994E-2</v>
-          </cell>
-          <cell r="I38">
-            <v>2.8269680638351402</v>
-          </cell>
-          <cell r="J38">
-            <v>2.70775958413298</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39">
-            <v>70182</v>
-          </cell>
-          <cell r="F39">
-            <v>6.7896282051281995E-2</v>
-          </cell>
-          <cell r="G39">
-            <v>6.7984871794872004E-2</v>
-          </cell>
-          <cell r="I39">
-            <v>1.54808250688823</v>
-          </cell>
-          <cell r="J39">
-            <v>1.5017269718456701</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40">
-            <v>70191</v>
-          </cell>
-          <cell r="F40">
-            <v>8.8600555555556001E-2</v>
-          </cell>
-          <cell r="G40">
-            <v>8.8703222222222003E-2</v>
-          </cell>
-          <cell r="I40">
-            <v>2.4209910524764902</v>
-          </cell>
-          <cell r="J40">
-            <v>2.41866571642029</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41">
-            <v>70192</v>
-          </cell>
-          <cell r="F41">
-            <v>1.4552888888890001E-3</v>
-          </cell>
-          <cell r="G41">
-            <v>1.4584144444439999E-3</v>
-          </cell>
-          <cell r="I41">
-            <v>1.4086988725201699</v>
-          </cell>
-          <cell r="J41">
-            <v>1.43453004370523</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42">
-            <v>70201</v>
-          </cell>
-          <cell r="F42">
-            <v>2.1988888888888999E-2</v>
-          </cell>
-          <cell r="G42">
-            <v>2.1989188888889E-2</v>
-          </cell>
-          <cell r="I42">
-            <v>1.58708467658437</v>
-          </cell>
-          <cell r="J42">
-            <v>1.7053539762746699</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43">
-            <v>70202</v>
-          </cell>
-          <cell r="F43">
-            <v>3.6495307692308E-2</v>
-          </cell>
-          <cell r="G43">
-            <v>3.9160871794872001E-2</v>
-          </cell>
-          <cell r="I43">
-            <v>4.3628145809809098</v>
-          </cell>
-          <cell r="J43">
-            <v>4.7681947309025396</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44">
-            <v>70211</v>
-          </cell>
-          <cell r="F44">
-            <v>6.4750256410256002E-2</v>
-          </cell>
-          <cell r="G44">
-            <v>4.7820294871794997E-2</v>
-          </cell>
-          <cell r="I44">
-            <v>3.0251858292634402</v>
-          </cell>
-          <cell r="J44">
-            <v>3.10690270036201</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45">
-            <v>70212</v>
-          </cell>
-          <cell r="F45">
-            <v>3.7656756410260001E-3</v>
-          </cell>
-          <cell r="G45">
-            <v>3.7721461538459998E-3</v>
-          </cell>
-          <cell r="I45">
-            <v>2.25256742455722</v>
-          </cell>
-          <cell r="J45">
-            <v>2.3604883216010601</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46">
-            <v>70221</v>
-          </cell>
-          <cell r="F46">
-            <v>2.5215384615385E-2</v>
-          </cell>
-          <cell r="G46">
-            <v>2.5216794871795001E-2</v>
-          </cell>
-          <cell r="I46">
-            <v>2.1563276454933602</v>
-          </cell>
-          <cell r="J46">
-            <v>2.0840296606415301</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47">
-            <v>70222</v>
-          </cell>
-          <cell r="F47">
-            <v>9.1032333333332993E-2</v>
-          </cell>
-          <cell r="G47">
-            <v>9.1890555555556003E-2</v>
-          </cell>
-          <cell r="I47">
-            <v>2.1462294543016198</v>
-          </cell>
-          <cell r="J47">
-            <v>2.1758491854143398</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48">
-            <v>70231</v>
-          </cell>
-          <cell r="F48">
-            <v>8.4850769230768994E-2</v>
-          </cell>
-          <cell r="G48">
-            <v>8.4316923076922998E-2</v>
-          </cell>
-          <cell r="I48">
-            <v>2.67447829446118</v>
-          </cell>
-          <cell r="J48">
-            <v>2.7587960319075102</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49">
-            <v>70232</v>
-          </cell>
-          <cell r="F49">
-            <v>5.5543846153845999E-2</v>
-          </cell>
-          <cell r="G49">
-            <v>5.2518717948717999E-2</v>
-          </cell>
-          <cell r="I49">
-            <v>2.81196514644573</v>
-          </cell>
-          <cell r="J49">
-            <v>2.8565173591759501</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50">
-            <v>70241</v>
-          </cell>
-          <cell r="F50">
-            <v>2.7184948717948999E-2</v>
-          </cell>
-          <cell r="G50">
-            <v>2.7184948717948999E-2</v>
-          </cell>
-          <cell r="I50">
-            <v>1.7855594267309201</v>
-          </cell>
-          <cell r="J50">
-            <v>1.7855594267309201</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51">
-            <v>70242</v>
-          </cell>
-          <cell r="F51">
-            <v>2.5870128205128001E-2</v>
-          </cell>
-          <cell r="G51">
-            <v>2.5870128205128001E-2</v>
-          </cell>
-          <cell r="I51">
-            <v>3.5724723807982399</v>
-          </cell>
-          <cell r="J51">
-            <v>3.5724723807982399</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52">
-            <v>70251</v>
-          </cell>
-          <cell r="F52">
-            <v>3.7236666666667001E-2</v>
-          </cell>
-          <cell r="G52">
-            <v>3.6252333333332998E-2</v>
-          </cell>
-          <cell r="I52">
-            <v>2.9352113539645401</v>
-          </cell>
-          <cell r="J52">
-            <v>3.48054468552297</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53">
-            <v>70252</v>
-          </cell>
-          <cell r="F53">
-            <v>6.8521410256409995E-2</v>
-          </cell>
-          <cell r="G53">
-            <v>2.9480769230769002E-2</v>
-          </cell>
-          <cell r="I53">
-            <v>3.33218410389139</v>
-          </cell>
-          <cell r="J53">
-            <v>3.5583746277780102</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54">
-            <v>70261</v>
-          </cell>
-          <cell r="F54">
-            <v>5.5959444444444E-2</v>
-          </cell>
-          <cell r="G54">
-            <v>5.5861111111111E-2</v>
-          </cell>
-          <cell r="I54">
-            <v>2.7834570059394301</v>
-          </cell>
-          <cell r="J54">
-            <v>2.7186660719850901</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55">
-            <v>70262</v>
-          </cell>
-          <cell r="F55">
-            <v>2.9756666666669999E-3</v>
-          </cell>
-          <cell r="G55">
-            <v>2.9885384615379999E-3</v>
-          </cell>
-          <cell r="I55">
-            <v>1.92952983986335</v>
-          </cell>
-          <cell r="J55">
-            <v>1.96887587770739</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56">
-            <v>70271</v>
-          </cell>
-          <cell r="F56">
-            <v>4.3420769230768999E-2</v>
-          </cell>
-          <cell r="G56">
-            <v>4.3399487179487002E-2</v>
-          </cell>
-          <cell r="I56">
-            <v>1.75479913612602</v>
-          </cell>
-          <cell r="J56">
-            <v>1.9458161882953899</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57">
-            <v>70272</v>
-          </cell>
-          <cell r="F57">
-            <v>5.6079555555556E-2</v>
-          </cell>
-          <cell r="G57">
-            <v>5.5192777777778E-2</v>
-          </cell>
-          <cell r="I57">
-            <v>1.5900691903550801</v>
-          </cell>
-          <cell r="J57">
-            <v>1.8873953497237499</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58">
-            <v>70281</v>
-          </cell>
-          <cell r="F58">
-            <v>1.7792188888889001E-2</v>
-          </cell>
-          <cell r="G58">
-            <v>1.5368577777778E-2</v>
-          </cell>
-          <cell r="I58">
-            <v>2.0251484381691802</v>
-          </cell>
-          <cell r="J58">
-            <v>2.3447700090975601</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59">
-            <v>70282</v>
-          </cell>
-          <cell r="F59">
-            <v>2.1565388888888998E-2</v>
-          </cell>
-          <cell r="G59">
-            <v>2.1702366666667E-2</v>
-          </cell>
-          <cell r="I59">
-            <v>1.90741491367613</v>
-          </cell>
-          <cell r="J59">
-            <v>1.8469760699683999</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60">
-            <v>70291</v>
-          </cell>
-          <cell r="F60">
-            <v>5.5251153846153998E-2</v>
-          </cell>
-          <cell r="G60">
-            <v>5.6711333333333003E-2</v>
-          </cell>
-          <cell r="I60">
-            <v>2.7521958780463902</v>
-          </cell>
-          <cell r="J60">
-            <v>2.5590781941048402</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61">
-            <v>70292</v>
-          </cell>
-          <cell r="F61">
-            <v>3.9816794871795E-2</v>
-          </cell>
-          <cell r="G61">
-            <v>3.1358589743590001E-2</v>
-          </cell>
-          <cell r="I61">
-            <v>3.3078875776989398</v>
-          </cell>
-          <cell r="J61">
-            <v>3.37122785676203</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62">
-            <v>70301</v>
-          </cell>
-          <cell r="F62">
-            <v>7.2442820512820999E-2</v>
-          </cell>
-          <cell r="G62">
-            <v>7.2251282051282006E-2</v>
-          </cell>
-          <cell r="I62">
-            <v>3.6217260352332801</v>
-          </cell>
-          <cell r="J62">
-            <v>3.6217260352332801</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="B63">
-            <v>70302</v>
-          </cell>
-          <cell r="F63">
-            <v>2.9219102564103001E-2</v>
-          </cell>
-          <cell r="G63">
-            <v>2.7529102564103E-2</v>
-          </cell>
-          <cell r="I63">
-            <v>4.77625090434982</v>
-          </cell>
-          <cell r="J63">
-            <v>4.77625090434982</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B530A3B7-6FE0-7811-987D-61644AFC6828}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13592175" y="3062287"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="361637" cy="187872"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC85FC89-A705-7EE2-605D-6826CA3B69A8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1000125" y="3205162"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="center"/>
+                  </m:oMathParaPr>
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛃</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐑𝐓𝐑</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="5" name="TextBox 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC85FC89-A705-7EE2-605D-6826CA3B69A8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1000125" y="3205162"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛃</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐑𝐓𝐑</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="361637" cy="187872"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="TextBox 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DB5AAE1-8699-4782-86F7-0B6E3F09A826}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="981075" y="3762375"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="center"/>
+                  </m:oMathParaPr>
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛃</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐑𝐓𝐑</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="TextBox 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DB5AAE1-8699-4782-86F7-0B6E3F09A826}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="981075" y="3762375"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛃</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐑𝐓𝐑</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="361637" cy="187872"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="TextBox 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4200487-B29B-4EE8-9E03-D184F039D89A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="733425" y="919162"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="center"/>
+                  </m:oMathParaPr>
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛃</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐑𝐓𝐑</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="13" name="TextBox 12">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4200487-B29B-4EE8-9E03-D184F039D89A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="733425" y="919162"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛃</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐑𝐓𝐑</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="361637" cy="187872"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E01B1EF1-42A9-4D87-A305-CA7173F889E7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="981075" y="1466850"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="center"/>
+                  </m:oMathParaPr>
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛃</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐑𝐓𝐑</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="TextBox 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E01B1EF1-42A9-4D87-A305-CA7173F889E7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="981075" y="1466850"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛃</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐑𝐓𝐑</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>137583</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>3808</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="444500" cy="198003"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="TextBox 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18EC38A9-FAFF-470C-90B1-72CC21D94816}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="984250" y="5496558"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:sSub>
+                    <m:sSubPr>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:sSubPr>
+                    <m:e>
+                      <m:acc>
+                        <m:accPr>
+                          <m:chr m:val="̂"/>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:accPr>
+                        <m:e>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝐒</m:t>
+                          </m:r>
+                        </m:e>
+                      </m:acc>
+                    </m:e>
+                    <m:sub>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝐂𝐓</m:t>
+                      </m:r>
+                    </m:sub>
+                  </m:sSub>
+                </m:oMath>
+              </a14:m>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="TextBox 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18EC38A9-FAFF-470C-90B1-72CC21D94816}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="984250" y="5496558"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̂_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐂𝐓</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="361637" cy="187872"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="TextBox 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE44435-B0E2-4F47-943A-52AE6E5FFFF0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1000125" y="3205162"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="center"/>
+                  </m:oMathParaPr>
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛃</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐑𝐓𝐑</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="17" name="TextBox 16">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE44435-B0E2-4F47-943A-52AE6E5FFFF0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1000125" y="3205162"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛃</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐑𝐓𝐑</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="361637" cy="187872"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="TextBox 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785319B9-3DBD-4D3F-9C77-C4FAD2C93429}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="981075" y="3762375"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="center"/>
+                  </m:oMathParaPr>
+                  <m:oMath>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝛃</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐑𝐓𝐑</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="TextBox 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{785319B9-3DBD-4D3F-9C77-C4FAD2C93429}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="981075" y="3762375"/>
+              <a:ext cx="361637" cy="187872"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝛃</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐑𝐓𝐑</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-IN" sz="1200" b="1" i="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>148167</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="444500" cy="198003"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="TextBox 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319BE1F5-9B3E-48B7-83BD-DAAA549C9AE9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="994834" y="2973917"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:sSub>
+                    <m:sSubPr>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:sSubPr>
+                    <m:e>
+                      <m:acc>
+                        <m:accPr>
+                          <m:chr m:val="̂"/>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:accPr>
+                        <m:e>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝐒</m:t>
+                          </m:r>
+                        </m:e>
+                      </m:acc>
+                    </m:e>
+                    <m:sub>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝐂𝐓</m:t>
+                      </m:r>
+                    </m:sub>
+                  </m:sSub>
+                </m:oMath>
+              </a14:m>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="TextBox 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319BE1F5-9B3E-48B7-83BD-DAAA549C9AE9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="994834" y="2973917"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̂_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐂𝐓</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>137584</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>179917</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="444500" cy="198003"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="TextBox 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{314E418A-8C9D-474D-B2E3-791AEF332622}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="984251" y="1206500"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:sSub>
+                    <m:sSubPr>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:sSubPr>
+                    <m:e>
+                      <m:acc>
+                        <m:accPr>
+                          <m:chr m:val="̂"/>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:accPr>
+                        <m:e>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝐒</m:t>
+                          </m:r>
+                        </m:e>
+                      </m:acc>
+                    </m:e>
+                    <m:sub>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝐂𝐓</m:t>
+                      </m:r>
+                    </m:sub>
+                  </m:sSub>
+                </m:oMath>
+              </a14:m>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="TextBox 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{314E418A-8C9D-474D-B2E3-791AEF332622}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="984251" y="1206500"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̂_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐂𝐓</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="444500" cy="198003"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="TextBox 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8ABC911-F705-4830-AF55-76A0BC8C646A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="973667" y="3577167"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:sSub>
+                    <m:sSubPr>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:sSubPr>
+                    <m:e>
+                      <m:acc>
+                        <m:accPr>
+                          <m:chr m:val="̂"/>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:accPr>
+                        <m:e>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝐒</m:t>
+                          </m:r>
+                        </m:e>
+                      </m:acc>
+                    </m:e>
+                    <m:sub>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝐂𝐓</m:t>
+                      </m:r>
+                    </m:sub>
+                  </m:sSub>
+                </m:oMath>
+              </a14:m>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="TextBox 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8ABC911-F705-4830-AF55-76A0BC8C646A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="973667" y="3577167"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̂_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐂𝐓</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>169334</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>179917</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="444500" cy="198003"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="TextBox 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1950FCC6-AD0B-4AF5-9212-58D9B0A1F138}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1016001" y="6043084"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:sSub>
+                    <m:sSubPr>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:sSubPr>
+                    <m:e>
+                      <m:acc>
+                        <m:accPr>
+                          <m:chr m:val="̂"/>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:accPr>
+                        <m:e>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝐒</m:t>
+                          </m:r>
+                        </m:e>
+                      </m:acc>
+                    </m:e>
+                    <m:sub>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝐂𝐓</m:t>
+                      </m:r>
+                    </m:sub>
+                  </m:sSub>
+                </m:oMath>
+              </a14:m>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="TextBox 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1950FCC6-AD0B-4AF5-9212-58D9B0A1F138}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1016001" y="6043084"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̂_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐂𝐓</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>148167</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>10584</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="444500" cy="198003"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="TextBox 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7D3CDB7-C8B8-4729-B6D1-E54A1A7F189E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="994834" y="582084"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:sSub>
+                    <m:sSubPr>
+                      <m:ctrlPr>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="1">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                      </m:ctrlPr>
+                    </m:sSubPr>
+                    <m:e>
+                      <m:acc>
+                        <m:accPr>
+                          <m:chr m:val="̂"/>
+                          <m:ctrlPr>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                          </m:ctrlPr>
+                        </m:accPr>
+                        <m:e>
+                          <m:r>
+                            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            </a:rPr>
+                            <m:t>𝐒</m:t>
+                          </m:r>
+                        </m:e>
+                      </m:acc>
+                    </m:e>
+                    <m:sub>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        </a:rPr>
+                        <m:t>𝐂𝐓</m:t>
+                      </m:r>
+                    </m:sub>
+                  </m:sSub>
+                </m:oMath>
+              </a14:m>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="TextBox 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7D3CDB7-C8B8-4729-B6D1-E54A1A7F189E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="994834" y="582084"/>
+              <a:ext cx="444500" cy="198003"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> ̂_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1200" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐂𝐓</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1200" b="1" i="0"/>
+                <a:t> (g)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14683,64 +15933,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="I1" s="30" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="I1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="U1" s="30" t="s">
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="U1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="G2" s="33"/>
-      <c r="I2" s="31" t="s">
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="I2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="48"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="31" t="s">
+      <c r="O2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="33"/>
-      <c r="U2" s="31" t="s">
+      <c r="P2" s="47"/>
+      <c r="Q2" s="48"/>
+      <c r="U2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="32"/>
-      <c r="W2" s="33"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="48"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -20761,46 +22011,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37" t="s">
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="25" t="s">
         <v>109</v>
       </c>
@@ -22934,13 +24184,13 @@
         <f t="shared" si="0"/>
         <v>2.0084562935677517E-3</v>
       </c>
-      <c r="F59" s="22">
+      <c r="F59" s="30">
         <v>2.2275346153846E-2</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="30">
         <v>3.5380794871794997E-2</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="31">
         <f t="shared" si="1"/>
         <v>-0.58833872333275716</v>
       </c>
@@ -23208,46 +24458,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:72" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37" t="s">
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37" t="s">
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
     </row>
     <row r="3" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="20" t="s">
         <v>109</v>
       </c>
@@ -25733,4 +26983,1742 @@
     <ignoredError sqref="H66" evalError="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E3F64C-314D-41C9-9D40-F07182D29B3B}">
+  <dimension ref="A1:AD44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" customWidth="1"/>
+    <col min="20" max="20" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.5703125" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.7109375" customWidth="1"/>
+    <col min="26" max="26" width="13" customWidth="1"/>
+    <col min="27" max="27" width="18.5703125" customWidth="1"/>
+    <col min="28" max="28" width="9.7109375" customWidth="1"/>
+    <col min="29" max="29" width="13.7109375" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" customWidth="1"/>
+    <col min="31" max="31" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" s="44"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="J3" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="M3" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="N3" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="E4" s="40">
+        <f>(C4-D4)/C4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="H4" s="40">
+        <f>(F4-G4)/F4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="K4" s="40">
+        <f>(I4-J4)/I4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>3.12</v>
+      </c>
+      <c r="M4" s="1">
+        <v>3.12</v>
+      </c>
+      <c r="N4" s="40">
+        <f>(L4-M4)/L4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="42"/>
+      <c r="C5" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="E5" s="40">
+        <f>(C5-D5)/C5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="H5" s="40">
+        <f t="shared" ref="H5:H8" si="0">(F5-G5)/F5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="K5" s="40">
+        <f t="shared" ref="K5:K8" si="1">(I5-J5)/I5</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="N5" s="40">
+        <f t="shared" ref="N5:N8" si="2">(L5-M5)/L5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E7" s="40">
+        <f t="shared" ref="E7:E8" si="3">(C7-D7)/C7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H7" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="K7" s="40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2.93</v>
+      </c>
+      <c r="M7" s="1">
+        <v>2.93</v>
+      </c>
+      <c r="N7" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="42"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="E8" s="40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="H8" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="K8" s="40">
+        <f t="shared" si="1"/>
+        <v>-2.222222222222224E-2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="N8" s="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+    </row>
+    <row r="15" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="44"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="L15" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="M15" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A16" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="E16" s="41">
+        <f>(C16-D16)/C16</f>
+        <v>-2.4096385542168697E-2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="H16" s="41">
+        <f>(F16-G16)/F16</f>
+        <v>7.5187969924812095E-3</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="K16" s="41">
+        <f>(I16-J16)/I16</f>
+        <v>-1.8072289156626523E-2</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2.13</v>
+      </c>
+      <c r="N16" s="41">
+        <f>(L16-M16)/L16</f>
+        <v>-2.898550724637684E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="42"/>
+      <c r="C17" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="E17" s="41">
+        <f t="shared" ref="E17:E20" si="4">(C17-D17)/C17</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H17" s="41">
+        <f t="shared" ref="H17:H20" si="5">(F17-G17)/F17</f>
+        <v>-2.3809523809523832E-2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="K17" s="41">
+        <f t="shared" ref="K17:K20" si="6">(I17-J17)/I17</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="N17" s="41">
+        <f t="shared" ref="N17:N20" si="7">(L17-M17)/L17</f>
+        <v>-4.6511627906976785E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="23"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="E19" s="41">
+        <f t="shared" si="4"/>
+        <v>-2.6666666666666689E-2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="H19" s="41">
+        <f t="shared" si="5"/>
+        <v>8.1967213114754172E-3</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="K19" s="41">
+        <f t="shared" si="6"/>
+        <v>-6.944444444444451E-3</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="M19" s="1">
+        <v>1.87</v>
+      </c>
+      <c r="N19" s="41">
+        <f t="shared" si="7"/>
+        <v>-4.4692737430167634E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="42"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="E20" s="41">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="H20" s="41">
+        <f t="shared" si="5"/>
+        <v>-7.3170731707317138E-2</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="K20" s="41">
+        <f t="shared" si="6"/>
+        <v>2.3255813953488393E-2</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="N20" s="41">
+        <f t="shared" si="7"/>
+        <v>-9.3023255813953445E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D21" s="34"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="M27" s="43"/>
+      <c r="N27" s="43"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="J28" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="L28" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="M28" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="N28" s="29" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="E29" s="40">
+        <f>(C29-D29)/C29</f>
+        <v>0.13333333333333328</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="H29" s="40">
+        <f>(F29-G29)/F29</f>
+        <v>9.7560975609756059E-2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="K29" s="40">
+        <f>(I29-J29)/I29</f>
+        <v>7.999999999999996E-2</v>
+      </c>
+      <c r="L29" s="1">
+        <v>2.38</v>
+      </c>
+      <c r="M29" s="1">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="N29" s="40">
+        <f>(L29-M29)/L29</f>
+        <v>5.8823529411764573E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="42"/>
+      <c r="C30" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="E30" s="40">
+        <f t="shared" ref="E30:E33" si="8">(C30-D30)/C30</f>
+        <v>0.12500000000000011</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="H30" s="40">
+        <f t="shared" ref="H30:H33" si="9">(F30-G30)/F30</f>
+        <v>0.11428571428571424</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="K30" s="40">
+        <f t="shared" ref="K30:K33" si="10">(I30-J30)/I30</f>
+        <v>2.7777777777777804E-2</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="N30" s="40">
+        <f t="shared" ref="N30:N33" si="11">(L30-M30)/L30</f>
+        <v>-8.8235294117646967E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="E32" s="40">
+        <f t="shared" si="8"/>
+        <v>0.14285714285714296</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="H32" s="40">
+        <f t="shared" si="9"/>
+        <v>0.12500000000000011</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="K32" s="40">
+        <f t="shared" si="10"/>
+        <v>6.4516129032258118E-2</v>
+      </c>
+      <c r="L32" s="1">
+        <v>2.17</v>
+      </c>
+      <c r="M32" s="1">
+        <v>2.04</v>
+      </c>
+      <c r="N32" s="40">
+        <f t="shared" si="11"/>
+        <v>5.9907834101382444E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="42"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="E33" s="40">
+        <f t="shared" si="8"/>
+        <v>0.21621621621621626</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="H33" s="40">
+        <f t="shared" si="9"/>
+        <v>0.25000000000000006</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="K33" s="40">
+        <f t="shared" si="10"/>
+        <v>0.15624999999999997</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N33" s="40">
+        <f t="shared" si="11"/>
+        <v>3.4482758620689495E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D34" s="34"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:H27"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49DE409-8975-4B38-94DB-0488B0DC3CF5}">
+  <dimension ref="A1:AE10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C2" s="1">
+        <v>226</v>
+      </c>
+      <c r="D2" s="33">
+        <f>(B2/C2)*1024</f>
+        <v>5.1653097345132739</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="C3" s="1">
+        <v>233</v>
+      </c>
+      <c r="D3" s="33">
+        <f t="shared" ref="D3:D5" si="0">(B3/C3)*1024</f>
+        <v>5.1419742489270384</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="1">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="C4" s="1">
+        <v>587</v>
+      </c>
+      <c r="D4" s="33">
+        <f t="shared" si="0"/>
+        <v>7.3093015332197622</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3.28</v>
+      </c>
+      <c r="C5" s="1">
+        <v>456</v>
+      </c>
+      <c r="D5" s="33">
+        <f t="shared" si="0"/>
+        <v>7.3656140350877193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7">
+        <v>30501</v>
+      </c>
+      <c r="G7">
+        <v>30502</v>
+      </c>
+      <c r="H7">
+        <v>30503</v>
+      </c>
+      <c r="I7">
+        <v>30504</v>
+      </c>
+      <c r="J7">
+        <v>5051</v>
+      </c>
+      <c r="K7">
+        <v>30401</v>
+      </c>
+      <c r="L7">
+        <v>30402</v>
+      </c>
+      <c r="M7">
+        <v>30403</v>
+      </c>
+      <c r="N7">
+        <v>30404</v>
+      </c>
+      <c r="O7">
+        <v>5041</v>
+      </c>
+      <c r="P7">
+        <v>30301</v>
+      </c>
+      <c r="Q7">
+        <v>30302</v>
+      </c>
+      <c r="R7">
+        <v>30303</v>
+      </c>
+      <c r="S7">
+        <v>30304</v>
+      </c>
+      <c r="T7">
+        <v>5031</v>
+      </c>
+      <c r="U7">
+        <v>30201</v>
+      </c>
+      <c r="V7">
+        <v>30202</v>
+      </c>
+      <c r="W7">
+        <v>30203</v>
+      </c>
+      <c r="X7">
+        <v>30204</v>
+      </c>
+      <c r="Y7">
+        <v>5021</v>
+      </c>
+      <c r="Z7">
+        <v>30101</v>
+      </c>
+      <c r="AA7">
+        <v>30102</v>
+      </c>
+      <c r="AB7">
+        <v>30103</v>
+      </c>
+      <c r="AC7">
+        <v>30104</v>
+      </c>
+      <c r="AD7">
+        <v>5011</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8">
+        <v>30501</v>
+      </c>
+      <c r="G8">
+        <v>30502</v>
+      </c>
+      <c r="H8">
+        <v>30503</v>
+      </c>
+      <c r="I8">
+        <v>30504</v>
+      </c>
+      <c r="J8">
+        <v>5051</v>
+      </c>
+      <c r="K8">
+        <v>30401</v>
+      </c>
+      <c r="L8">
+        <v>30402</v>
+      </c>
+      <c r="M8">
+        <v>30403</v>
+      </c>
+      <c r="N8">
+        <v>30404</v>
+      </c>
+      <c r="O8">
+        <v>5041</v>
+      </c>
+      <c r="P8">
+        <v>30301</v>
+      </c>
+      <c r="Q8">
+        <v>30302</v>
+      </c>
+      <c r="R8">
+        <v>30303</v>
+      </c>
+      <c r="S8">
+        <v>30304</v>
+      </c>
+      <c r="T8">
+        <v>5031</v>
+      </c>
+      <c r="U8">
+        <v>30201</v>
+      </c>
+      <c r="V8">
+        <v>30202</v>
+      </c>
+      <c r="W8">
+        <v>30203</v>
+      </c>
+      <c r="X8">
+        <v>30204</v>
+      </c>
+      <c r="Y8">
+        <v>5021</v>
+      </c>
+      <c r="Z8">
+        <v>30101</v>
+      </c>
+      <c r="AA8">
+        <v>30102</v>
+      </c>
+      <c r="AB8">
+        <v>30103</v>
+      </c>
+      <c r="AC8">
+        <v>30104</v>
+      </c>
+      <c r="AD8">
+        <v>5011</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9">
+        <v>6011</v>
+      </c>
+      <c r="G9">
+        <v>6012</v>
+      </c>
+      <c r="H9">
+        <v>6021</v>
+      </c>
+      <c r="I9">
+        <v>6022</v>
+      </c>
+      <c r="J9">
+        <v>6031</v>
+      </c>
+      <c r="K9">
+        <v>6032</v>
+      </c>
+      <c r="L9">
+        <v>6041</v>
+      </c>
+      <c r="M9">
+        <v>6042</v>
+      </c>
+      <c r="N9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F10">
+        <v>40601</v>
+      </c>
+      <c r="G10">
+        <v>40602</v>
+      </c>
+      <c r="H10">
+        <v>40603</v>
+      </c>
+      <c r="I10">
+        <v>40604</v>
+      </c>
+      <c r="J10">
+        <v>40501</v>
+      </c>
+      <c r="K10">
+        <v>40502</v>
+      </c>
+      <c r="L10">
+        <v>40503</v>
+      </c>
+      <c r="M10">
+        <v>40504</v>
+      </c>
+      <c r="N10">
+        <v>40401</v>
+      </c>
+      <c r="O10">
+        <v>40402</v>
+      </c>
+      <c r="P10">
+        <v>40403</v>
+      </c>
+      <c r="Q10">
+        <v>40404</v>
+      </c>
+      <c r="R10">
+        <v>40301</v>
+      </c>
+      <c r="S10">
+        <v>40302</v>
+      </c>
+      <c r="T10">
+        <v>40303</v>
+      </c>
+      <c r="U10">
+        <v>40304</v>
+      </c>
+      <c r="V10">
+        <v>40201</v>
+      </c>
+      <c r="W10">
+        <v>40202</v>
+      </c>
+      <c r="X10">
+        <v>40203</v>
+      </c>
+      <c r="Y10">
+        <v>40204</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8017FF1D-E816-4B42-B22F-2A4022E2054D}">
+  <dimension ref="A2:S56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="D3" s="37">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2.7349999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="D4" s="37">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2.173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C5" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D5" s="37">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2.867</v>
+      </c>
+      <c r="J5" s="36"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="D6" s="37">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1.9330000000000001</v>
+      </c>
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="D7" s="37">
+        <v>0.32</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3.2160000000000002</v>
+      </c>
+      <c r="J7" s="36"/>
+      <c r="S7" s="36"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C8" s="1">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="D8" s="37">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3.0590000000000002</v>
+      </c>
+      <c r="J8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="S8" s="36"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C9" s="1">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="D9" s="37">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.8479999999999999</v>
+      </c>
+      <c r="J9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="S9" s="36"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="D10" s="37">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2.4470000000000001</v>
+      </c>
+      <c r="J10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="S10" s="36"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C11" s="1">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="D11" s="37">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2.5070000000000001</v>
+      </c>
+      <c r="J11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="S11" s="36"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="D12" s="37">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.825</v>
+      </c>
+      <c r="J12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="S12" s="36"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C13" s="1">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="D13" s="37">
+        <v>0.74099999999999999</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2.734</v>
+      </c>
+      <c r="J13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="S13" s="36"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C14" s="1">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3.0750000000000002</v>
+      </c>
+      <c r="J14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="S14" s="36"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="S15" s="36"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="J16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="S16" s="36"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" t="s">
+        <v>158</v>
+      </c>
+      <c r="J17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="S17" s="36"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2.4470000000000001</v>
+      </c>
+      <c r="L18" s="36"/>
+      <c r="S18" s="36"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="L19" s="36"/>
+      <c r="S19" s="36"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="L20" s="36"/>
+      <c r="S20" s="36"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S21" s="36"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S22" s="36"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S23" s="36"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E24" s="36"/>
+      <c r="S24" s="36"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E25" s="36"/>
+      <c r="S25" s="36"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E26" s="36"/>
+      <c r="S26" s="36"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E27" s="36"/>
+      <c r="S27" s="36"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E28" s="36"/>
+      <c r="S28" s="36"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E29" s="36"/>
+      <c r="S29" s="36"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E30" s="36"/>
+      <c r="S30" s="36"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E31" s="36"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="E32" s="36"/>
+    </row>
+    <row r="33" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E33" s="36"/>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E34" s="36"/>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E35" s="36"/>
+    </row>
+    <row r="36" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E36" s="36"/>
+    </row>
+    <row r="44" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="L44" s="36"/>
+    </row>
+    <row r="45" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="L45" s="36"/>
+    </row>
+    <row r="46" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="L46" s="36"/>
+    </row>
+    <row r="47" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="L47" s="36"/>
+    </row>
+    <row r="48" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="L48" s="36"/>
+    </row>
+    <row r="49" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L49" s="36"/>
+    </row>
+    <row r="50" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L50" s="36"/>
+    </row>
+    <row r="51" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L51" s="36"/>
+    </row>
+    <row r="52" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L52" s="36"/>
+    </row>
+    <row r="53" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L53" s="36"/>
+    </row>
+    <row r="54" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L54" s="36"/>
+    </row>
+    <row r="55" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L55" s="36"/>
+    </row>
+    <row r="56" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L56" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
+++ b/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\StaticDynamicAnalysis\ida-spo-msa\HazardAnalysis\gm-selection\2020_NBC_MyCopy_new-main\GMSelection_NGA_KiK_mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11366C7-5392-4258-9E8C-349CBB882B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C912AD-16E7-48B2-BA05-4B97A44D987D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,9 +492,6 @@
     <t>MIDR (%)</t>
   </si>
   <si>
-    <t>RDR (%)</t>
-  </si>
-  <si>
     <t>AllComp</t>
   </si>
   <si>
@@ -570,9 +567,6 @@
     <t>CollapseMechanism, 12 (%)</t>
   </si>
   <si>
-    <t>PFA (%)</t>
-  </si>
-  <si>
     <t>0.2g</t>
   </si>
   <si>
@@ -595,6 +589,12 @@
   </si>
   <si>
     <t>1) Not much significant variation in median capacity between original and curtailed GMs</t>
+  </si>
+  <si>
+    <t>MRDR (%)</t>
+  </si>
+  <si>
+    <t>MPFA (%)</t>
   </si>
 </sst>
 </file>
@@ -1047,10 +1047,11 @@
     <xf numFmtId="10" fontId="13" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyFont="1" applyAlignment="1">
@@ -1080,7 +1081,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Calculation" xfId="4" builtinId="22"/>
@@ -15933,64 +15933,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="I1" s="45" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="I1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="45" t="s">
+      <c r="O1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="U1" s="45" t="s">
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="U1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="I2" s="46" t="s">
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="I2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="47"/>
-      <c r="K2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-      <c r="O2" s="46" t="s">
+      <c r="O2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="48"/>
-      <c r="U2" s="46" t="s">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="49"/>
+      <c r="U2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="47"/>
-      <c r="W2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="49"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -22011,46 +22011,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
     </row>
     <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52" t="s">
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="25" t="s">
         <v>109</v>
       </c>
@@ -24458,46 +24458,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
     </row>
     <row r="2" spans="1:72" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52" t="s">
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="20" t="s">
         <v>109</v>
       </c>
@@ -27034,29 +27034,29 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="44" t="s">
         <v>137</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D2" s="43"/>
       <c r="E2" s="43"/>
       <c r="F2" s="43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G2" s="43"/>
       <c r="H2" s="43"/>
       <c r="I2" s="43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J2" s="43"/>
       <c r="K2" s="43"/>
       <c r="L2" s="43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M2" s="43"/>
       <c r="N2" s="43"/>
@@ -27065,8 +27065,8 @@
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="44"/>
-      <c r="B3" s="42"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="44"/>
       <c r="C3" s="38" t="s">
         <v>109</v>
       </c>
@@ -27108,8 +27108,8 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>139</v>
+      <c r="A4" s="44" t="s">
+        <v>138</v>
       </c>
       <c r="C4" s="1">
         <v>0.31</v>
@@ -27153,7 +27153,7 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42"/>
+      <c r="A5" s="44"/>
       <c r="C5" s="1">
         <v>0.49</v>
       </c>
@@ -27211,8 +27211,8 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
-        <v>161</v>
+      <c r="A7" s="44" t="s">
+        <v>160</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="1">
@@ -27257,7 +27257,7 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42"/>
+      <c r="A8" s="44"/>
       <c r="B8" s="39"/>
       <c r="C8" s="1">
         <v>0.46</v>
@@ -27325,36 +27325,36 @@
       <c r="AD9" s="1"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="42" t="s">
-        <v>138</v>
+      <c r="B14" s="44" t="s">
+        <v>171</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="43"/>
       <c r="E14" s="43"/>
       <c r="F14" s="43" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G14" s="43"/>
       <c r="H14" s="43"/>
       <c r="I14" s="43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J14" s="43"/>
       <c r="K14" s="43"/>
       <c r="L14" s="43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M14" s="43"/>
       <c r="N14" s="43"/>
     </row>
     <row r="15" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
-      <c r="B15" s="42"/>
+      <c r="A15" s="45"/>
+      <c r="B15" s="44"/>
       <c r="C15" s="38" t="s">
         <v>109</v>
       </c>
@@ -27393,8 +27393,8 @@
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
-        <v>139</v>
+      <c r="A16" s="44" t="s">
+        <v>138</v>
       </c>
       <c r="C16" s="1">
         <v>0.83</v>
@@ -27438,7 +27438,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="42"/>
+      <c r="A17" s="44"/>
       <c r="C17" s="1">
         <v>0.46</v>
       </c>
@@ -27496,8 +27496,8 @@
       <c r="N18" s="23"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
-        <v>161</v>
+      <c r="A19" s="44" t="s">
+        <v>160</v>
       </c>
       <c r="B19" s="39"/>
       <c r="C19" s="1">
@@ -27542,7 +27542,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="39"/>
       <c r="C20" s="1">
         <v>0.48</v>
@@ -27599,36 +27599,36 @@
       <c r="N21" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="42" t="s">
-        <v>164</v>
+      <c r="B27" s="44" t="s">
+        <v>172</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D27" s="43"/>
       <c r="E27" s="43"/>
       <c r="F27" s="43" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G27" s="43"/>
       <c r="H27" s="43"/>
       <c r="I27" s="43" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J27" s="43"/>
       <c r="K27" s="43"/>
       <c r="L27" s="43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M27" s="43"/>
       <c r="N27" s="43"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="42"/>
+      <c r="A28" s="45"/>
+      <c r="B28" s="44"/>
       <c r="C28" s="38" t="s">
         <v>109</v>
       </c>
@@ -27667,8 +27667,8 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="42" t="s">
-        <v>139</v>
+      <c r="A29" s="44" t="s">
+        <v>138</v>
       </c>
       <c r="C29" s="1">
         <v>0.15</v>
@@ -27712,7 +27712,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="42"/>
+      <c r="A30" s="44"/>
       <c r="C30" s="1">
         <v>0.4</v>
       </c>
@@ -27770,8 +27770,8 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
-        <v>161</v>
+      <c r="A32" s="44" t="s">
+        <v>160</v>
       </c>
       <c r="B32" s="39"/>
       <c r="C32" s="1">
@@ -27816,7 +27816,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="42"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="39"/>
       <c r="C33" s="1">
         <v>0.37</v>
@@ -27873,41 +27873,46 @@
       <c r="N34" s="1"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="42" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="42" t="s">
         <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="42" t="s">
         <v>107</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="53" t="s">
-        <v>169</v>
+      <c r="A44" s="42" t="s">
+        <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A2:A3"/>
@@ -27915,17 +27920,12 @@
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="L14:N14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:E27"/>
     <mergeCell ref="F27:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28329,24 +28329,24 @@
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="E2" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B3" s="1">
         <v>1.84</v>
@@ -28363,7 +28363,7 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="1">
         <v>1.84</v>
@@ -28380,7 +28380,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B5" s="1">
         <v>1.84</v>
@@ -28398,7 +28398,7 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1">
         <v>1.84</v>
@@ -28416,7 +28416,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B7" s="1">
         <v>1.84</v>
@@ -28435,7 +28435,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B8" s="1">
         <v>1.84</v>
@@ -28455,7 +28455,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B9" s="1">
         <v>1.84</v>
@@ -28495,7 +28495,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B11" s="1">
         <v>1.84</v>
@@ -28515,7 +28515,7 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B12" s="1">
         <v>1.84</v>
@@ -28585,16 +28585,16 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" t="s">
         <v>144</v>
       </c>
-      <c r="B17" t="s">
-        <v>145</v>
-      </c>
       <c r="C17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J17" s="36"/>
       <c r="L17" s="36"/>

--- a/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
+++ b/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/30GM_1p84_SF5_Guw_diffDeltaM.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C912AD-16E7-48B2-BA05-4B97A44D987D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GMSel_ΔM (±)" sheetId="1" r:id="rId1"/>
@@ -1048,10 +1048,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyFont="1" applyAlignment="1">
@@ -27037,36 +27037,36 @@
       <c r="A2" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43" t="s">
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43" t="s">
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43" t="s">
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
-      <c r="B3" s="44"/>
+      <c r="B3" s="43"/>
       <c r="C3" s="38" t="s">
         <v>109</v>
       </c>
@@ -27108,7 +27108,7 @@
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="43" t="s">
         <v>138</v>
       </c>
       <c r="C4" s="1">
@@ -27153,7 +27153,7 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+      <c r="A5" s="43"/>
       <c r="C5" s="1">
         <v>0.49</v>
       </c>
@@ -27211,7 +27211,7 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="43" t="s">
         <v>160</v>
       </c>
       <c r="B7" s="39"/>
@@ -27257,7 +27257,7 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+      <c r="A8" s="43"/>
       <c r="B8" s="39"/>
       <c r="C8" s="1">
         <v>0.46</v>
@@ -27328,33 +27328,33 @@
       <c r="A14" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43" t="s">
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43" t="s">
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43" t="s">
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
     </row>
     <row r="15" spans="1:30" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45"/>
-      <c r="B15" s="44"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="38" t="s">
         <v>109</v>
       </c>
@@ -27393,7 +27393,7 @@
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="43" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="1">
@@ -27438,7 +27438,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+      <c r="A17" s="43"/>
       <c r="C17" s="1">
         <v>0.46</v>
       </c>
@@ -27496,7 +27496,7 @@
       <c r="N18" s="23"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="43" t="s">
         <v>160</v>
       </c>
       <c r="B19" s="39"/>
@@ -27542,7 +27542,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
+      <c r="A20" s="43"/>
       <c r="B20" s="39"/>
       <c r="C20" s="1">
         <v>0.48</v>
@@ -27602,33 +27602,33 @@
       <c r="A27" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43" t="s">
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43" t="s">
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43" t="s">
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="45"/>
-      <c r="B28" s="44"/>
+      <c r="B28" s="43"/>
       <c r="C28" s="38" t="s">
         <v>109</v>
       </c>
@@ -27667,7 +27667,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="44" t="s">
+      <c r="A29" s="43" t="s">
         <v>138</v>
       </c>
       <c r="C29" s="1">
@@ -27712,7 +27712,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
+      <c r="A30" s="43"/>
       <c r="C30" s="1">
         <v>0.4</v>
       </c>
@@ -27770,7 +27770,7 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="43" t="s">
         <v>160</v>
       </c>
       <c r="B32" s="39"/>
@@ -27816,7 +27816,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="39"/>
       <c r="C33" s="1">
         <v>0.37</v>
@@ -27903,16 +27903,12 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="A2:A3"/>
@@ -27920,13 +27916,17 @@
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="F27:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
